--- a/examples/auto.xlsx
+++ b/examples/auto.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10309"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macbook/Desktop/ДИПЛОМ/RegressionAnalysis/examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{62242700-B8B5-2F44-A071-BF5E98509BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15BE957C-9C8D-5344-9786-BBB88C69BD75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4440" yWindow="920" windowWidth="25800" windowHeight="17240" xr2:uid="{D2C2347C-DC86-874D-BAE3-67A054A0DE71}"/>
   </bookViews>
@@ -93,10 +93,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -444,10 +443,10 @@
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -455,13 +454,13 @@
       <c r="A2" s="1">
         <v>480</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2">
         <v>1993</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2">
         <v>0</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2">
         <v>150000</v>
       </c>
     </row>
@@ -469,13 +468,13 @@
       <c r="A3" s="1">
         <v>18300</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3">
         <v>2011</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3">
         <v>190</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3">
         <v>125000</v>
       </c>
     </row>
@@ -483,13 +482,13 @@
       <c r="A4" s="1">
         <v>9800</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4">
         <v>2004</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4">
         <v>163</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4">
         <v>125000</v>
       </c>
     </row>
@@ -497,13 +496,13 @@
       <c r="A5" s="1">
         <v>1500</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5">
         <v>2001</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5">
         <v>75</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5">
         <v>150000</v>
       </c>
     </row>
@@ -511,13 +510,13 @@
       <c r="A6" s="1">
         <v>3600</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6">
         <v>2008</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6">
         <v>69</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6">
         <v>90000</v>
       </c>
     </row>
@@ -525,13 +524,13 @@
       <c r="A7" s="1">
         <v>650</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7">
         <v>1995</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7">
         <v>102</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7">
         <v>150000</v>
       </c>
     </row>
@@ -539,13 +538,13 @@
       <c r="A8" s="1">
         <v>2200</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8">
         <v>2004</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8">
         <v>109</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8">
         <v>150000</v>
       </c>
     </row>
@@ -553,13 +552,13 @@
       <c r="A9" s="1">
         <v>0</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9">
         <v>1980</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9">
         <v>50</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9">
         <v>40000</v>
       </c>
     </row>
@@ -567,13 +566,13 @@
       <c r="A10" s="1">
         <v>14500</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10">
         <v>2014</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10">
         <v>125</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10">
         <v>30000</v>
       </c>
     </row>
@@ -581,13 +580,13 @@
       <c r="A11" s="1">
         <v>999</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11">
         <v>1998</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11">
         <v>101</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11">
         <v>150000</v>
       </c>
     </row>
@@ -595,13 +594,13 @@
       <c r="A12" s="1">
         <v>2000</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12">
         <v>2004</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12">
         <v>105</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12">
         <v>150000</v>
       </c>
     </row>
@@ -609,13 +608,13 @@
       <c r="A13" s="1">
         <v>2799</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13">
         <v>2005</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13">
         <v>140</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13">
         <v>150000</v>
       </c>
     </row>
@@ -623,13 +622,13 @@
       <c r="A14" s="1">
         <v>999</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14">
         <v>1995</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14">
         <v>115</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14">
         <v>150000</v>
       </c>
     </row>
@@ -637,13 +636,13 @@
       <c r="A15" s="1">
         <v>2500</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15">
         <v>2004</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15">
         <v>131</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15">
         <v>150000</v>
       </c>
     </row>
@@ -651,13 +650,13 @@
       <c r="A16" s="1">
         <v>17999</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16">
         <v>2011</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16">
         <v>190</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16">
         <v>70000</v>
       </c>
     </row>
@@ -665,13 +664,13 @@
       <c r="A17" s="1">
         <v>450</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17">
         <v>1910</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17">
         <v>0</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17">
         <v>5000</v>
       </c>
     </row>
@@ -679,13 +678,13 @@
       <c r="A18" s="1">
         <v>300</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18">
         <v>2016</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18">
         <v>60</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18">
         <v>150000</v>
       </c>
     </row>
@@ -693,13 +692,13 @@
       <c r="A19" s="1">
         <v>1750</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19">
         <v>2004</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19">
         <v>75</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19">
         <v>150000</v>
       </c>
     </row>
@@ -707,13 +706,13 @@
       <c r="A20" s="1">
         <v>7550</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20">
         <v>2007</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20">
         <v>136</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20">
         <v>150000</v>
       </c>
     </row>
@@ -721,13 +720,13 @@
       <c r="A21" s="1">
         <v>1850</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21">
         <v>2004</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21">
         <v>102</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21">
         <v>150000</v>
       </c>
     </row>
@@ -735,13 +734,13 @@
       <c r="A22" s="1">
         <v>10400</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22">
         <v>2009</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22">
         <v>160</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22">
         <v>100000</v>
       </c>
     </row>
@@ -749,13 +748,13 @@
       <c r="A23" s="1">
         <v>3699</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23">
         <v>2002</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23">
         <v>231</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23">
         <v>150000</v>
       </c>
     </row>
@@ -763,13 +762,13 @@
       <c r="A24" s="1">
         <v>2900</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24">
         <v>2018</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24">
         <v>90</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24">
         <v>150000</v>
       </c>
     </row>
@@ -777,13 +776,13 @@
       <c r="A25" s="1">
         <v>450</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25">
         <v>1997</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25">
         <v>50</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25">
         <v>150000</v>
       </c>
     </row>
@@ -791,13 +790,13 @@
       <c r="A26" s="1">
         <v>500</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26">
         <v>1990</v>
       </c>
-      <c r="C26" s="2">
+      <c r="C26">
         <v>118</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26">
         <v>150000</v>
       </c>
     </row>
@@ -805,13 +804,13 @@
       <c r="A27" s="1">
         <v>2500</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27">
         <v>2002</v>
       </c>
-      <c r="C27" s="2">
+      <c r="C27">
         <v>193</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27">
         <v>150000</v>
       </c>
     </row>
@@ -819,13 +818,13 @@
       <c r="A28" s="1">
         <v>5555</v>
       </c>
-      <c r="B28" s="2">
+      <c r="B28">
         <v>2017</v>
       </c>
-      <c r="C28" s="2">
+      <c r="C28">
         <v>125</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D28">
         <v>125000</v>
       </c>
     </row>
@@ -833,13 +832,13 @@
       <c r="A29" s="1">
         <v>6900</v>
       </c>
-      <c r="B29" s="2">
+      <c r="B29">
         <v>2008</v>
       </c>
-      <c r="C29" s="2">
+      <c r="C29">
         <v>99</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29">
         <v>60000</v>
       </c>
     </row>
@@ -847,13 +846,13 @@
       <c r="A30" s="1">
         <v>1990</v>
       </c>
-      <c r="B30" s="2">
+      <c r="B30">
         <v>1981</v>
       </c>
-      <c r="C30" s="2">
+      <c r="C30">
         <v>50</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D30">
         <v>5000</v>
       </c>
     </row>
@@ -861,13 +860,13 @@
       <c r="A31" s="1">
         <v>690</v>
       </c>
-      <c r="B31" s="2">
+      <c r="B31">
         <v>2003</v>
       </c>
-      <c r="C31" s="2">
+      <c r="C31">
         <v>60</v>
       </c>
-      <c r="D31" s="2">
+      <c r="D31">
         <v>150000</v>
       </c>
     </row>
@@ -875,13 +874,13 @@
       <c r="A32" s="1">
         <v>3300</v>
       </c>
-      <c r="B32" s="2">
+      <c r="B32">
         <v>1995</v>
       </c>
-      <c r="C32" s="2">
+      <c r="C32">
         <v>113</v>
       </c>
-      <c r="D32" s="2">
+      <c r="D32">
         <v>150000</v>
       </c>
     </row>
@@ -889,13 +888,13 @@
       <c r="A33" s="1">
         <v>899</v>
       </c>
-      <c r="B33" s="2">
+      <c r="B33">
         <v>2016</v>
       </c>
-      <c r="C33" s="2">
+      <c r="C33">
         <v>60</v>
       </c>
-      <c r="D33" s="2">
+      <c r="D33">
         <v>150000</v>
       </c>
     </row>
@@ -903,13 +902,13 @@
       <c r="A34" s="1">
         <v>245</v>
       </c>
-      <c r="B34" s="2">
+      <c r="B34">
         <v>1994</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C34">
         <v>0</v>
       </c>
-      <c r="D34" s="2">
+      <c r="D34">
         <v>150000</v>
       </c>
     </row>
@@ -917,13 +916,13 @@
       <c r="A35" s="1">
         <v>18000</v>
       </c>
-      <c r="B35" s="2">
+      <c r="B35">
         <v>2007</v>
       </c>
-      <c r="C35" s="2">
+      <c r="C35">
         <v>218</v>
       </c>
-      <c r="D35" s="2">
+      <c r="D35">
         <v>20000</v>
       </c>
     </row>
@@ -931,13 +930,13 @@
       <c r="A36" s="1">
         <v>3500</v>
       </c>
-      <c r="B36" s="2">
+      <c r="B36">
         <v>2004</v>
       </c>
-      <c r="C36" s="2">
+      <c r="C36">
         <v>122</v>
       </c>
-      <c r="D36" s="2">
+      <c r="D36">
         <v>150000</v>
       </c>
     </row>
@@ -945,13 +944,13 @@
       <c r="A37" s="1">
         <v>350</v>
       </c>
-      <c r="B37" s="2">
+      <c r="B37">
         <v>2016</v>
       </c>
-      <c r="C37" s="2">
+      <c r="C37">
         <v>75</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D37">
         <v>150000</v>
       </c>
     </row>
@@ -959,13 +958,13 @@
       <c r="A38" s="1">
         <v>1600</v>
       </c>
-      <c r="B38" s="2">
+      <c r="B38">
         <v>1991</v>
       </c>
-      <c r="C38" s="2">
+      <c r="C38">
         <v>75</v>
       </c>
-      <c r="D38" s="2">
+      <c r="D38">
         <v>70000</v>
       </c>
     </row>
@@ -973,13 +972,13 @@
       <c r="A39" s="1">
         <v>1500</v>
       </c>
-      <c r="B39" s="2">
+      <c r="B39">
         <v>2016</v>
       </c>
-      <c r="C39" s="2">
+      <c r="C39">
         <v>0</v>
       </c>
-      <c r="D39" s="2">
+      <c r="D39">
         <v>150000</v>
       </c>
     </row>
@@ -987,13 +986,13 @@
       <c r="A40" s="1">
         <v>11900</v>
       </c>
-      <c r="B40" s="2">
+      <c r="B40">
         <v>2002</v>
       </c>
-      <c r="C40" s="2">
+      <c r="C40">
         <v>129</v>
       </c>
-      <c r="D40" s="2">
+      <c r="D40">
         <v>150000</v>
       </c>
     </row>
@@ -1001,13 +1000,13 @@
       <c r="A41" s="1">
         <v>1500</v>
       </c>
-      <c r="B41" s="2">
+      <c r="B41">
         <v>1984</v>
       </c>
-      <c r="C41" s="2">
+      <c r="C41">
         <v>70</v>
       </c>
-      <c r="D41" s="2">
+      <c r="D41">
         <v>150000</v>
       </c>
     </row>
@@ -1015,13 +1014,13 @@
       <c r="A42" s="1">
         <v>0</v>
       </c>
-      <c r="B42" s="2">
+      <c r="B42">
         <v>1990</v>
       </c>
-      <c r="C42" s="2">
+      <c r="C42">
         <v>0</v>
       </c>
-      <c r="D42" s="2">
+      <c r="D42">
         <v>150000</v>
       </c>
     </row>
@@ -1029,13 +1028,13 @@
       <c r="A43" s="1">
         <v>7500</v>
       </c>
-      <c r="B43" s="2">
+      <c r="B43">
         <v>2002</v>
       </c>
-      <c r="C43" s="2">
+      <c r="C43">
         <v>306</v>
       </c>
-      <c r="D43" s="2">
+      <c r="D43">
         <v>150000</v>
       </c>
     </row>
@@ -1043,13 +1042,13 @@
       <c r="A44" s="1">
         <v>12500</v>
       </c>
-      <c r="B44" s="2">
+      <c r="B44">
         <v>2006</v>
       </c>
-      <c r="C44" s="2">
+      <c r="C44">
         <v>231</v>
       </c>
-      <c r="D44" s="2">
+      <c r="D44">
         <v>150000</v>
       </c>
     </row>
@@ -1057,13 +1056,13 @@
       <c r="A45" s="1">
         <v>6990</v>
       </c>
-      <c r="B45" s="2">
+      <c r="B45">
         <v>2007</v>
       </c>
-      <c r="C45" s="2">
+      <c r="C45">
         <v>95</v>
       </c>
-      <c r="D45" s="2">
+      <c r="D45">
         <v>100000</v>
       </c>
     </row>
@@ -1071,13 +1070,13 @@
       <c r="A46" s="1">
         <v>3900</v>
       </c>
-      <c r="B46" s="2">
+      <c r="B46">
         <v>2008</v>
       </c>
-      <c r="C46" s="2">
+      <c r="C46">
         <v>61</v>
       </c>
-      <c r="D46" s="2">
+      <c r="D46">
         <v>80000</v>
       </c>
     </row>
@@ -1085,13 +1084,13 @@
       <c r="A47" s="1">
         <v>590</v>
       </c>
-      <c r="B47" s="2">
+      <c r="B47">
         <v>1999</v>
       </c>
-      <c r="C47" s="2">
+      <c r="C47">
         <v>75</v>
       </c>
-      <c r="D47" s="2">
+      <c r="D47">
         <v>125000</v>
       </c>
     </row>
@@ -1099,13 +1098,13 @@
       <c r="A48" s="1">
         <v>7999</v>
       </c>
-      <c r="B48" s="2">
+      <c r="B48">
         <v>2007</v>
       </c>
-      <c r="C48" s="2">
+      <c r="C48">
         <v>177</v>
       </c>
-      <c r="D48" s="2">
+      <c r="D48">
         <v>150000</v>
       </c>
     </row>
@@ -1113,13 +1112,13 @@
       <c r="A49" s="1">
         <v>2100</v>
       </c>
-      <c r="B49" s="2">
+      <c r="B49">
         <v>1998</v>
       </c>
-      <c r="C49" s="2">
+      <c r="C49">
         <v>193</v>
       </c>
-      <c r="D49" s="2">
+      <c r="D49">
         <v>150000</v>
       </c>
     </row>
@@ -1127,13 +1126,13 @@
       <c r="A50" s="1">
         <v>7750</v>
       </c>
-      <c r="B50" s="2">
+      <c r="B50">
         <v>2017</v>
       </c>
-      <c r="C50" s="2">
+      <c r="C50">
         <v>80</v>
       </c>
-      <c r="D50" s="2">
+      <c r="D50">
         <v>100000</v>
       </c>
     </row>
@@ -1141,13 +1140,13 @@
       <c r="A51" s="1">
         <v>13500</v>
       </c>
-      <c r="B51" s="2">
+      <c r="B51">
         <v>2012</v>
       </c>
-      <c r="C51" s="2">
+      <c r="C51">
         <v>109</v>
       </c>
-      <c r="D51" s="2">
+      <c r="D51">
         <v>150000</v>
       </c>
     </row>
@@ -1155,13 +1154,13 @@
       <c r="A52" s="1">
         <v>14800</v>
       </c>
-      <c r="B52" s="2">
+      <c r="B52">
         <v>2008</v>
       </c>
-      <c r="C52" s="2">
+      <c r="C52">
         <v>170</v>
       </c>
-      <c r="D52" s="2">
+      <c r="D52">
         <v>125000</v>
       </c>
     </row>
@@ -1169,13 +1168,13 @@
       <c r="A53" s="1">
         <v>2000</v>
       </c>
-      <c r="B53" s="2">
+      <c r="B53">
         <v>2017</v>
       </c>
-      <c r="C53" s="2">
+      <c r="C53">
         <v>90</v>
       </c>
-      <c r="D53" s="2">
+      <c r="D53">
         <v>150000</v>
       </c>
     </row>
@@ -1183,13 +1182,13 @@
       <c r="A54" s="1">
         <v>1400</v>
       </c>
-      <c r="B54" s="2">
+      <c r="B54">
         <v>2016</v>
       </c>
-      <c r="C54" s="2">
+      <c r="C54">
         <v>55</v>
       </c>
-      <c r="D54" s="2">
+      <c r="D54">
         <v>5000</v>
       </c>
     </row>
@@ -1197,13 +1196,13 @@
       <c r="A55" s="1">
         <v>7999</v>
       </c>
-      <c r="B55" s="2">
+      <c r="B55">
         <v>2008</v>
       </c>
-      <c r="C55" s="2">
+      <c r="C55">
         <v>143</v>
       </c>
-      <c r="D55" s="2">
+      <c r="D55">
         <v>150000</v>
       </c>
     </row>
@@ -1211,13 +1210,13 @@
       <c r="A56" s="1">
         <v>4700</v>
       </c>
-      <c r="B56" s="2">
+      <c r="B56">
         <v>2005</v>
       </c>
-      <c r="C56" s="2">
+      <c r="C56">
         <v>0</v>
       </c>
-      <c r="D56" s="2">
+      <c r="D56">
         <v>150000</v>
       </c>
     </row>
@@ -1225,13 +1224,13 @@
       <c r="A57" s="1">
         <v>550</v>
       </c>
-      <c r="B57" s="2">
+      <c r="B57">
         <v>1999</v>
       </c>
-      <c r="C57" s="2">
+      <c r="C57">
         <v>0</v>
       </c>
-      <c r="D57" s="2">
+      <c r="D57">
         <v>150000</v>
       </c>
     </row>
@@ -1239,13 +1238,13 @@
       <c r="A58" s="1">
         <v>3000</v>
       </c>
-      <c r="B58" s="2">
+      <c r="B58">
         <v>2006</v>
       </c>
-      <c r="C58" s="2">
+      <c r="C58">
         <v>61</v>
       </c>
-      <c r="D58" s="2">
+      <c r="D58">
         <v>80000</v>
       </c>
     </row>
@@ -1253,13 +1252,13 @@
       <c r="A59" s="1">
         <v>2399</v>
       </c>
-      <c r="B59" s="2">
+      <c r="B59">
         <v>2018</v>
       </c>
-      <c r="C59" s="2">
+      <c r="C59">
         <v>64</v>
       </c>
-      <c r="D59" s="2">
+      <c r="D59">
         <v>125000</v>
       </c>
     </row>
@@ -1267,13 +1266,13 @@
       <c r="A60" s="1">
         <v>1000</v>
       </c>
-      <c r="B60" s="2">
+      <c r="B60">
         <v>1998</v>
       </c>
-      <c r="C60" s="2">
+      <c r="C60">
         <v>101</v>
       </c>
-      <c r="D60" s="2">
+      <c r="D60">
         <v>150000</v>
       </c>
     </row>
@@ -1281,13 +1280,13 @@
       <c r="A61" s="1">
         <v>1</v>
       </c>
-      <c r="B61" s="2">
+      <c r="B61">
         <v>1994</v>
       </c>
-      <c r="C61" s="2">
+      <c r="C61">
         <v>286</v>
       </c>
-      <c r="D61" s="2">
+      <c r="D61">
         <v>150000</v>
       </c>
     </row>
@@ -1295,13 +1294,13 @@
       <c r="A62" s="1">
         <v>200</v>
       </c>
-      <c r="B62" s="2">
+      <c r="B62">
         <v>1995</v>
       </c>
-      <c r="C62" s="2">
+      <c r="C62">
         <v>102</v>
       </c>
-      <c r="D62" s="2">
+      <c r="D62">
         <v>150000</v>
       </c>
     </row>
@@ -1309,13 +1308,13 @@
       <c r="A63" s="1">
         <v>7499</v>
       </c>
-      <c r="B63" s="2">
+      <c r="B63">
         <v>2004</v>
       </c>
-      <c r="C63" s="2">
+      <c r="C63">
         <v>232</v>
       </c>
-      <c r="D63" s="2">
+      <c r="D63">
         <v>150000</v>
       </c>
     </row>
@@ -1323,13 +1322,13 @@
       <c r="A64" s="1">
         <v>5500</v>
       </c>
-      <c r="B64" s="2">
+      <c r="B64">
         <v>2010</v>
       </c>
-      <c r="C64" s="2">
+      <c r="C64">
         <v>60</v>
       </c>
-      <c r="D64" s="2">
+      <c r="D64">
         <v>70000</v>
       </c>
     </row>
@@ -1337,13 +1336,13 @@
       <c r="A65" s="1">
         <v>7000</v>
       </c>
-      <c r="B65" s="2">
+      <c r="B65">
         <v>2006</v>
       </c>
-      <c r="C65" s="2">
+      <c r="C65">
         <v>105</v>
       </c>
-      <c r="D65" s="2">
+      <c r="D65">
         <v>100000</v>
       </c>
     </row>
@@ -1351,13 +1350,13 @@
       <c r="A66" s="1">
         <v>14999</v>
       </c>
-      <c r="B66" s="2">
+      <c r="B66">
         <v>2007</v>
       </c>
-      <c r="C66" s="2">
+      <c r="C66">
         <v>218</v>
       </c>
-      <c r="D66" s="2">
+      <c r="D66">
         <v>50000</v>
       </c>
     </row>
@@ -1365,13 +1364,13 @@
       <c r="A67" s="1">
         <v>10900</v>
       </c>
-      <c r="B67" s="2">
+      <c r="B67">
         <v>2017</v>
       </c>
-      <c r="C67" s="2">
+      <c r="C67">
         <v>101</v>
       </c>
-      <c r="D67" s="2">
+      <c r="D67">
         <v>50000</v>
       </c>
     </row>
@@ -1379,13 +1378,13 @@
       <c r="A68" s="1">
         <v>9700</v>
       </c>
-      <c r="B68" s="2">
+      <c r="B68">
         <v>2008</v>
       </c>
-      <c r="C68" s="2">
+      <c r="C68">
         <v>160</v>
       </c>
-      <c r="D68" s="2">
+      <c r="D68">
         <v>150000</v>
       </c>
     </row>
@@ -1393,13 +1392,13 @@
       <c r="A69" s="1">
         <v>2100</v>
       </c>
-      <c r="B69" s="2">
+      <c r="B69">
         <v>2000</v>
       </c>
-      <c r="C69" s="2">
+      <c r="C69">
         <v>105</v>
       </c>
-      <c r="D69" s="2">
+      <c r="D69">
         <v>150000</v>
       </c>
     </row>
@@ -1407,13 +1406,13 @@
       <c r="A70" s="1">
         <v>1280</v>
       </c>
-      <c r="B70" s="2">
+      <c r="B70">
         <v>1992</v>
       </c>
-      <c r="C70" s="2">
+      <c r="C70">
         <v>109</v>
       </c>
-      <c r="D70" s="2">
+      <c r="D70">
         <v>150000</v>
       </c>
     </row>
@@ -1421,13 +1420,13 @@
       <c r="A71" s="1">
         <v>1200</v>
       </c>
-      <c r="B71" s="2">
+      <c r="B71">
         <v>2001</v>
       </c>
-      <c r="C71" s="2">
+      <c r="C71">
         <v>0</v>
       </c>
-      <c r="D71" s="2">
+      <c r="D71">
         <v>150000</v>
       </c>
     </row>
@@ -1435,13 +1434,13 @@
       <c r="A72" s="1">
         <v>800</v>
       </c>
-      <c r="B72" s="2">
+      <c r="B72">
         <v>1993</v>
       </c>
-      <c r="C72" s="2">
+      <c r="C72">
         <v>0</v>
       </c>
-      <c r="D72" s="2">
+      <c r="D72">
         <v>150000</v>
       </c>
     </row>
@@ -1449,13 +1448,13 @@
       <c r="A73" s="1">
         <v>2300</v>
       </c>
-      <c r="B73" s="2">
+      <c r="B73">
         <v>1997</v>
       </c>
-      <c r="C73" s="2">
+      <c r="C73">
         <v>150</v>
       </c>
-      <c r="D73" s="2">
+      <c r="D73">
         <v>150000</v>
       </c>
     </row>
@@ -1463,13 +1462,13 @@
       <c r="A74" s="1">
         <v>750</v>
       </c>
-      <c r="B74" s="2">
+      <c r="B74">
         <v>2002</v>
       </c>
-      <c r="C74" s="2">
+      <c r="C74">
         <v>50</v>
       </c>
-      <c r="D74" s="2">
+      <c r="D74">
         <v>150000</v>
       </c>
     </row>
@@ -1477,13 +1476,13 @@
       <c r="A75" s="1">
         <v>7999</v>
       </c>
-      <c r="B75" s="2">
+      <c r="B75">
         <v>2008</v>
       </c>
-      <c r="C75" s="2">
+      <c r="C75">
         <v>156</v>
       </c>
-      <c r="D75" s="2">
+      <c r="D75">
         <v>150000</v>
       </c>
     </row>
@@ -1491,13 +1490,13 @@
       <c r="A76" s="1">
         <v>6600</v>
       </c>
-      <c r="B76" s="2">
+      <c r="B76">
         <v>2006</v>
       </c>
-      <c r="C76" s="2">
+      <c r="C76">
         <v>105</v>
       </c>
-      <c r="D76" s="2">
+      <c r="D76">
         <v>150000</v>
       </c>
     </row>
@@ -1505,13 +1504,13 @@
       <c r="A77" s="1">
         <v>7999</v>
       </c>
-      <c r="B77" s="2">
+      <c r="B77">
         <v>2013</v>
       </c>
-      <c r="C77" s="2">
+      <c r="C77">
         <v>80</v>
       </c>
-      <c r="D77" s="2">
+      <c r="D77">
         <v>40000</v>
       </c>
     </row>
@@ -1519,13 +1518,13 @@
       <c r="A78" s="1">
         <v>1400</v>
       </c>
-      <c r="B78" s="2">
+      <c r="B78">
         <v>2003</v>
       </c>
-      <c r="C78" s="2">
+      <c r="C78">
         <v>82</v>
       </c>
-      <c r="D78" s="2">
+      <c r="D78">
         <v>150000</v>
       </c>
     </row>
@@ -1533,13 +1532,13 @@
       <c r="A79" s="1">
         <v>800</v>
       </c>
-      <c r="B79" s="2">
+      <c r="B79">
         <v>2000</v>
       </c>
-      <c r="C79" s="2">
+      <c r="C79">
         <v>90</v>
       </c>
-      <c r="D79" s="2">
+      <c r="D79">
         <v>150000</v>
       </c>
     </row>
@@ -1547,13 +1546,13 @@
       <c r="A80" s="1">
         <v>5000</v>
       </c>
-      <c r="B80" s="2">
+      <c r="B80">
         <v>2006</v>
       </c>
-      <c r="C80" s="2">
+      <c r="C80">
         <v>109</v>
       </c>
-      <c r="D80" s="2">
+      <c r="D80">
         <v>150000</v>
       </c>
     </row>
@@ -1561,13 +1560,13 @@
       <c r="A81" s="1">
         <v>150</v>
       </c>
-      <c r="B81" s="2">
+      <c r="B81">
         <v>2016</v>
       </c>
-      <c r="C81" s="2">
+      <c r="C81">
         <v>75</v>
       </c>
-      <c r="D81" s="2">
+      <c r="D81">
         <v>150000</v>
       </c>
     </row>
@@ -1575,13 +1574,13 @@
       <c r="A82" s="1">
         <v>250</v>
       </c>
-      <c r="B82" s="2">
+      <c r="B82">
         <v>2000</v>
       </c>
-      <c r="C82" s="2">
+      <c r="C82">
         <v>155</v>
       </c>
-      <c r="D82" s="2">
+      <c r="D82">
         <v>150000</v>
       </c>
     </row>
@@ -1589,13 +1588,13 @@
       <c r="A83" s="1">
         <v>350</v>
       </c>
-      <c r="B83" s="2">
+      <c r="B83">
         <v>1997</v>
       </c>
-      <c r="C83" s="2">
+      <c r="C83">
         <v>54</v>
       </c>
-      <c r="D83" s="2">
+      <c r="D83">
         <v>150000</v>
       </c>
     </row>
@@ -1603,13 +1602,13 @@
       <c r="A84" s="1">
         <v>600</v>
       </c>
-      <c r="B84" s="2">
+      <c r="B84">
         <v>1994</v>
       </c>
-      <c r="C84" s="2">
+      <c r="C84">
         <v>75</v>
       </c>
-      <c r="D84" s="2">
+      <c r="D84">
         <v>100000</v>
       </c>
     </row>
@@ -1617,13 +1616,13 @@
       <c r="A85" s="1">
         <v>3300</v>
       </c>
-      <c r="B85" s="2">
+      <c r="B85">
         <v>2005</v>
       </c>
-      <c r="C85" s="2">
+      <c r="C85">
         <v>150</v>
       </c>
-      <c r="D85" s="2">
+      <c r="D85">
         <v>150000</v>
       </c>
     </row>
@@ -1631,13 +1630,13 @@
       <c r="A86" s="1">
         <v>1600</v>
       </c>
-      <c r="B86" s="2">
+      <c r="B86">
         <v>1997</v>
       </c>
-      <c r="C86" s="2">
+      <c r="C86">
         <v>122</v>
       </c>
-      <c r="D86" s="2">
+      <c r="D86">
         <v>150000</v>
       </c>
     </row>
@@ -1645,13 +1644,13 @@
       <c r="A87" s="1">
         <v>8000</v>
       </c>
-      <c r="B87" s="2">
+      <c r="B87">
         <v>2005</v>
       </c>
-      <c r="C87" s="2">
+      <c r="C87">
         <v>185</v>
       </c>
-      <c r="D87" s="2">
+      <c r="D87">
         <v>150000</v>
       </c>
     </row>
@@ -1659,13 +1658,13 @@
       <c r="A88" s="1">
         <v>1800</v>
       </c>
-      <c r="B88" s="2">
+      <c r="B88">
         <v>2001</v>
       </c>
-      <c r="C88" s="2">
+      <c r="C88">
         <v>87</v>
       </c>
-      <c r="D88" s="2">
+      <c r="D88">
         <v>150000</v>
       </c>
     </row>
@@ -1673,13 +1672,13 @@
       <c r="A89" s="1">
         <v>6800</v>
       </c>
-      <c r="B89" s="2">
+      <c r="B89">
         <v>2009</v>
       </c>
-      <c r="C89" s="2">
+      <c r="C89">
         <v>82</v>
       </c>
-      <c r="D89" s="2">
+      <c r="D89">
         <v>60000</v>
       </c>
     </row>
@@ -1687,13 +1686,13 @@
       <c r="A90" s="1">
         <v>2990</v>
       </c>
-      <c r="B90" s="2">
+      <c r="B90">
         <v>2004</v>
       </c>
-      <c r="C90" s="2">
+      <c r="C90">
         <v>113</v>
       </c>
-      <c r="D90" s="2">
+      <c r="D90">
         <v>150000</v>
       </c>
     </row>
@@ -1701,13 +1700,13 @@
       <c r="A91" s="1">
         <v>1</v>
       </c>
-      <c r="B91" s="2">
+      <c r="B91">
         <v>1995</v>
       </c>
-      <c r="C91" s="2">
+      <c r="C91">
         <v>113</v>
       </c>
-      <c r="D91" s="2">
+      <c r="D91">
         <v>150000</v>
       </c>
     </row>
@@ -1715,13 +1714,13 @@
       <c r="A92" s="1">
         <v>2400</v>
       </c>
-      <c r="B92" s="2">
+      <c r="B92">
         <v>2003</v>
       </c>
-      <c r="C92" s="2">
+      <c r="C92">
         <v>0</v>
       </c>
-      <c r="D92" s="2">
+      <c r="D92">
         <v>150000</v>
       </c>
     </row>
@@ -1729,13 +1728,13 @@
       <c r="A93" s="1">
         <v>1222</v>
       </c>
-      <c r="B93" s="2">
+      <c r="B93">
         <v>1984</v>
       </c>
-      <c r="C93" s="2">
+      <c r="C93">
         <v>180</v>
       </c>
-      <c r="D93" s="2">
+      <c r="D93">
         <v>150000</v>
       </c>
     </row>
@@ -1743,13 +1742,13 @@
       <c r="A94" s="1">
         <v>250</v>
       </c>
-      <c r="B94" s="2">
+      <c r="B94">
         <v>2000</v>
       </c>
-      <c r="C94" s="2">
+      <c r="C94">
         <v>60</v>
       </c>
-      <c r="D94" s="2">
+      <c r="D94">
         <v>150000</v>
       </c>
     </row>
@@ -1757,13 +1756,13 @@
       <c r="A95" s="1">
         <v>14500</v>
       </c>
-      <c r="B95" s="2">
+      <c r="B95">
         <v>2013</v>
       </c>
-      <c r="C95" s="2">
+      <c r="C95">
         <v>86</v>
       </c>
-      <c r="D95" s="2">
+      <c r="D95">
         <v>60000</v>
       </c>
     </row>
@@ -1771,13 +1770,13 @@
       <c r="A96" s="1">
         <v>8390</v>
       </c>
-      <c r="B96" s="2">
+      <c r="B96">
         <v>2009</v>
       </c>
-      <c r="C96" s="2">
+      <c r="C96">
         <v>0</v>
       </c>
-      <c r="D96" s="2">
+      <c r="D96">
         <v>150000</v>
       </c>
     </row>
@@ -1785,13 +1784,13 @@
       <c r="A97" s="1">
         <v>3850</v>
       </c>
-      <c r="B97" s="2">
+      <c r="B97">
         <v>2003</v>
       </c>
-      <c r="C97" s="2">
+      <c r="C97">
         <v>131</v>
       </c>
-      <c r="D97" s="2">
+      <c r="D97">
         <v>150000</v>
       </c>
     </row>
@@ -1799,13 +1798,13 @@
       <c r="A98" s="1">
         <v>6450</v>
       </c>
-      <c r="B98" s="2">
+      <c r="B98">
         <v>2008</v>
       </c>
-      <c r="C98" s="2">
+      <c r="C98">
         <v>84</v>
       </c>
-      <c r="D98" s="2">
+      <c r="D98">
         <v>150000</v>
       </c>
     </row>
@@ -1813,13 +1812,13 @@
       <c r="A99" s="1">
         <v>1700</v>
       </c>
-      <c r="B99" s="2">
+      <c r="B99">
         <v>1999</v>
       </c>
-      <c r="C99" s="2">
+      <c r="C99">
         <v>102</v>
       </c>
-      <c r="D99" s="2">
+      <c r="D99">
         <v>125000</v>
       </c>
     </row>
@@ -1827,13 +1826,13 @@
       <c r="A100" s="1">
         <v>4290</v>
       </c>
-      <c r="B100" s="2">
+      <c r="B100">
         <v>2008</v>
       </c>
-      <c r="C100" s="2">
+      <c r="C100">
         <v>0</v>
       </c>
-      <c r="D100" s="2">
+      <c r="D100">
         <v>150000</v>
       </c>
     </row>
@@ -1841,13 +1840,13 @@
       <c r="A101" s="1">
         <v>1500</v>
       </c>
-      <c r="B101" s="2">
+      <c r="B101">
         <v>2006</v>
       </c>
-      <c r="C101" s="2">
+      <c r="C101">
         <v>109</v>
       </c>
-      <c r="D101" s="2">
+      <c r="D101">
         <v>150000</v>
       </c>
     </row>
@@ -1855,13 +1854,13 @@
       <c r="A102" s="1">
         <v>499</v>
       </c>
-      <c r="B102" s="2">
+      <c r="B102">
         <v>1995</v>
       </c>
-      <c r="C102" s="2">
+      <c r="C102">
         <v>101</v>
       </c>
-      <c r="D102" s="2">
+      <c r="D102">
         <v>150000</v>
       </c>
     </row>
@@ -1869,13 +1868,13 @@
       <c r="A103" s="1">
         <v>6500</v>
       </c>
-      <c r="B103" s="2">
+      <c r="B103">
         <v>2004</v>
       </c>
-      <c r="C103" s="2">
+      <c r="C103">
         <v>163</v>
       </c>
-      <c r="D103" s="2">
+      <c r="D103">
         <v>150000</v>
       </c>
     </row>
@@ -1883,13 +1882,13 @@
       <c r="A104" s="1">
         <v>900</v>
       </c>
-      <c r="B104" s="2">
+      <c r="B104">
         <v>1999</v>
       </c>
-      <c r="C104" s="2">
+      <c r="C104">
         <v>125</v>
       </c>
-      <c r="D104" s="2">
+      <c r="D104">
         <v>150000</v>
       </c>
     </row>
@@ -1897,13 +1896,13 @@
       <c r="A105" s="1">
         <v>650</v>
       </c>
-      <c r="B105" s="2">
+      <c r="B105">
         <v>1997</v>
       </c>
-      <c r="C105" s="2">
+      <c r="C105">
         <v>102</v>
       </c>
-      <c r="D105" s="2">
+      <c r="D105">
         <v>150000</v>
       </c>
     </row>
@@ -1911,13 +1910,13 @@
       <c r="A106" s="1">
         <v>300</v>
       </c>
-      <c r="B106" s="2">
+      <c r="B106">
         <v>1992</v>
       </c>
-      <c r="C106" s="2">
+      <c r="C106">
         <v>105</v>
       </c>
-      <c r="D106" s="2">
+      <c r="D106">
         <v>150000</v>
       </c>
     </row>
@@ -1925,13 +1924,13 @@
       <c r="A107" s="1">
         <v>3399</v>
       </c>
-      <c r="B107" s="2">
+      <c r="B107">
         <v>1999</v>
       </c>
-      <c r="C107" s="2">
+      <c r="C107">
         <v>224</v>
       </c>
-      <c r="D107" s="2">
+      <c r="D107">
         <v>150000</v>
       </c>
     </row>
@@ -1939,13 +1938,13 @@
       <c r="A108" s="1">
         <v>1300</v>
       </c>
-      <c r="B108" s="2">
+      <c r="B108">
         <v>1997</v>
       </c>
-      <c r="C108" s="2">
+      <c r="C108">
         <v>101</v>
       </c>
-      <c r="D108" s="2">
+      <c r="D108">
         <v>150000</v>
       </c>
     </row>
@@ -1953,13 +1952,13 @@
       <c r="A109" s="1">
         <v>900</v>
       </c>
-      <c r="B109" s="2">
+      <c r="B109">
         <v>1995</v>
       </c>
-      <c r="C109" s="2">
+      <c r="C109">
         <v>90</v>
       </c>
-      <c r="D109" s="2">
+      <c r="D109">
         <v>150000</v>
       </c>
     </row>
@@ -1967,13 +1966,13 @@
       <c r="A110" s="1">
         <v>7300</v>
       </c>
-      <c r="B110" s="2">
+      <c r="B110">
         <v>2009</v>
       </c>
-      <c r="C110" s="2">
+      <c r="C110">
         <v>235</v>
       </c>
-      <c r="D110" s="2">
+      <c r="D110">
         <v>100000</v>
       </c>
     </row>
@@ -1981,13 +1980,13 @@
       <c r="A111" s="1">
         <v>8599</v>
       </c>
-      <c r="B111" s="2">
+      <c r="B111">
         <v>2006</v>
       </c>
-      <c r="C111" s="2">
+      <c r="C111">
         <v>200</v>
       </c>
-      <c r="D111" s="2">
+      <c r="D111">
         <v>125000</v>
       </c>
     </row>
@@ -1995,13 +1994,13 @@
       <c r="A112" s="1">
         <v>350</v>
       </c>
-      <c r="B112" s="2">
+      <c r="B112">
         <v>1998</v>
       </c>
-      <c r="C112" s="2">
+      <c r="C112">
         <v>0</v>
       </c>
-      <c r="D112" s="2">
+      <c r="D112">
         <v>150000</v>
       </c>
     </row>
@@ -2009,13 +2008,13 @@
       <c r="A113" s="1">
         <v>0</v>
       </c>
-      <c r="B113" s="2">
+      <c r="B113">
         <v>2017</v>
       </c>
-      <c r="C113" s="2">
+      <c r="C113">
         <v>0</v>
       </c>
-      <c r="D113" s="2">
+      <c r="D113">
         <v>5000</v>
       </c>
     </row>
@@ -2023,13 +2022,13 @@
       <c r="A114" s="1">
         <v>5900</v>
       </c>
-      <c r="B114" s="2">
+      <c r="B114">
         <v>2005</v>
       </c>
-      <c r="C114" s="2">
+      <c r="C114">
         <v>178</v>
       </c>
-      <c r="D114" s="2">
+      <c r="D114">
         <v>150000</v>
       </c>
     </row>
@@ -2037,13 +2036,13 @@
       <c r="A115" s="1">
         <v>6300</v>
       </c>
-      <c r="B115" s="2">
+      <c r="B115">
         <v>2002</v>
       </c>
-      <c r="C115" s="2">
+      <c r="C115">
         <v>265</v>
       </c>
-      <c r="D115" s="2">
+      <c r="D115">
         <v>150000</v>
       </c>
     </row>
@@ -2051,13 +2050,13 @@
       <c r="A116" s="1">
         <v>3500</v>
       </c>
-      <c r="B116" s="2">
+      <c r="B116">
         <v>1991</v>
       </c>
-      <c r="C116" s="2">
+      <c r="C116">
         <v>160</v>
       </c>
-      <c r="D116" s="2">
+      <c r="D116">
         <v>150000</v>
       </c>
     </row>
@@ -2065,13 +2064,13 @@
       <c r="A117" s="1">
         <v>0</v>
       </c>
-      <c r="B117" s="2">
+      <c r="B117">
         <v>1999</v>
       </c>
-      <c r="C117" s="2">
+      <c r="C117">
         <v>0</v>
       </c>
-      <c r="D117" s="2">
+      <c r="D117">
         <v>5000</v>
       </c>
     </row>
@@ -2079,13 +2078,13 @@
       <c r="A118" s="1">
         <v>5950</v>
       </c>
-      <c r="B118" s="2">
+      <c r="B118">
         <v>2006</v>
       </c>
-      <c r="C118" s="2">
+      <c r="C118">
         <v>163</v>
       </c>
-      <c r="D118" s="2">
+      <c r="D118">
         <v>150000</v>
       </c>
     </row>
@@ -2093,13 +2092,13 @@
       <c r="A119" s="1">
         <v>1699</v>
       </c>
-      <c r="B119" s="2">
+      <c r="B119">
         <v>2003</v>
       </c>
-      <c r="C119" s="2">
+      <c r="C119">
         <v>77</v>
       </c>
-      <c r="D119" s="2">
+      <c r="D119">
         <v>150000</v>
       </c>
     </row>
@@ -2107,13 +2106,13 @@
       <c r="A120" s="1">
         <v>4699</v>
       </c>
-      <c r="B120" s="2">
+      <c r="B120">
         <v>1996</v>
       </c>
-      <c r="C120" s="2">
+      <c r="C120">
         <v>110</v>
       </c>
-      <c r="D120" s="2">
+      <c r="D120">
         <v>150000</v>
       </c>
     </row>
@@ -2121,13 +2120,13 @@
       <c r="A121" s="1">
         <v>400</v>
       </c>
-      <c r="B121" s="2">
+      <c r="B121">
         <v>2000</v>
       </c>
-      <c r="C121" s="2">
+      <c r="C121">
         <v>144</v>
       </c>
-      <c r="D121" s="2">
+      <c r="D121">
         <v>150000</v>
       </c>
     </row>
@@ -2135,13 +2134,13 @@
       <c r="A122" s="1">
         <v>9290</v>
       </c>
-      <c r="B122" s="2">
+      <c r="B122">
         <v>2010</v>
       </c>
-      <c r="C122" s="2">
+      <c r="C122">
         <v>86</v>
       </c>
-      <c r="D122" s="2">
+      <c r="D122">
         <v>40000</v>
       </c>
     </row>
@@ -2149,13 +2148,13 @@
       <c r="A123" s="1">
         <v>7000</v>
       </c>
-      <c r="B123" s="2">
+      <c r="B123">
         <v>2003</v>
       </c>
-      <c r="C123" s="2">
+      <c r="C123">
         <v>120</v>
       </c>
-      <c r="D123" s="2">
+      <c r="D123">
         <v>150000</v>
       </c>
     </row>
@@ -2163,13 +2162,13 @@
       <c r="A124" s="1">
         <v>1199</v>
       </c>
-      <c r="B124" s="2">
+      <c r="B124">
         <v>2000</v>
       </c>
-      <c r="C124" s="2">
+      <c r="C124">
         <v>60</v>
       </c>
-      <c r="D124" s="2">
+      <c r="D124">
         <v>150000</v>
       </c>
     </row>
@@ -2177,13 +2176,13 @@
       <c r="A125" s="1">
         <v>1750</v>
       </c>
-      <c r="B125" s="2">
+      <c r="B125">
         <v>2002</v>
       </c>
-      <c r="C125" s="2">
+      <c r="C125">
         <v>75</v>
       </c>
-      <c r="D125" s="2">
+      <c r="D125">
         <v>125000</v>
       </c>
     </row>
@@ -2191,13 +2190,13 @@
       <c r="A126" s="1">
         <v>1000</v>
       </c>
-      <c r="B126" s="2">
+      <c r="B126">
         <v>1990</v>
       </c>
-      <c r="C126" s="2">
+      <c r="C126">
         <v>54</v>
       </c>
-      <c r="D126" s="2">
+      <c r="D126">
         <v>150000</v>
       </c>
     </row>
@@ -2205,13 +2204,13 @@
       <c r="A127" s="1">
         <v>1800</v>
       </c>
-      <c r="B127" s="2">
+      <c r="B127">
         <v>1995</v>
       </c>
-      <c r="C127" s="2">
+      <c r="C127">
         <v>286</v>
       </c>
-      <c r="D127" s="2">
+      <c r="D127">
         <v>150000</v>
       </c>
     </row>
@@ -2219,13 +2218,13 @@
       <c r="A128" s="1">
         <v>8000</v>
       </c>
-      <c r="B128" s="2">
+      <c r="B128">
         <v>2009</v>
       </c>
-      <c r="C128" s="2">
+      <c r="C128">
         <v>0</v>
       </c>
-      <c r="D128" s="2">
+      <c r="D128">
         <v>100000</v>
       </c>
     </row>
@@ -2233,13 +2232,13 @@
       <c r="A129" s="1">
         <v>1100</v>
       </c>
-      <c r="B129" s="2">
+      <c r="B129">
         <v>2003</v>
       </c>
-      <c r="C129" s="2">
+      <c r="C129">
         <v>75</v>
       </c>
-      <c r="D129" s="2">
+      <c r="D129">
         <v>150000</v>
       </c>
     </row>
@@ -2247,13 +2246,13 @@
       <c r="A130" s="1">
         <v>2990</v>
       </c>
-      <c r="B130" s="2">
+      <c r="B130">
         <v>2001</v>
       </c>
-      <c r="C130" s="2">
+      <c r="C130">
         <v>170</v>
       </c>
-      <c r="D130" s="2">
+      <c r="D130">
         <v>150000</v>
       </c>
     </row>
@@ -2261,13 +2260,13 @@
       <c r="A131" s="1">
         <v>300</v>
       </c>
-      <c r="B131" s="2">
+      <c r="B131">
         <v>2000</v>
       </c>
-      <c r="C131" s="2">
+      <c r="C131">
         <v>54</v>
       </c>
-      <c r="D131" s="2">
+      <c r="D131">
         <v>150000</v>
       </c>
     </row>
@@ -2275,13 +2274,13 @@
       <c r="A132" s="1">
         <v>3390</v>
       </c>
-      <c r="B132" s="2">
+      <c r="B132">
         <v>2000</v>
       </c>
-      <c r="C132" s="2">
+      <c r="C132">
         <v>0</v>
       </c>
-      <c r="D132" s="2">
+      <c r="D132">
         <v>150000</v>
       </c>
     </row>
@@ -2289,13 +2288,13 @@
       <c r="A133" s="1">
         <v>2750</v>
       </c>
-      <c r="B133" s="2">
+      <c r="B133">
         <v>2001</v>
       </c>
-      <c r="C133" s="2">
+      <c r="C133">
         <v>131</v>
       </c>
-      <c r="D133" s="2">
+      <c r="D133">
         <v>150000</v>
       </c>
     </row>
@@ -2303,13 +2302,13 @@
       <c r="A134" s="1">
         <v>6990</v>
       </c>
-      <c r="B134" s="2">
+      <c r="B134">
         <v>2012</v>
       </c>
-      <c r="C134" s="2">
+      <c r="C134">
         <v>75</v>
       </c>
-      <c r="D134" s="2">
+      <c r="D134">
         <v>100000</v>
       </c>
     </row>
@@ -2317,13 +2316,13 @@
       <c r="A135" s="1">
         <v>4800</v>
       </c>
-      <c r="B135" s="2">
+      <c r="B135">
         <v>1996</v>
       </c>
-      <c r="C135" s="2">
+      <c r="C135">
         <v>116</v>
       </c>
-      <c r="D135" s="2">
+      <c r="D135">
         <v>150000</v>
       </c>
     </row>
@@ -2331,13 +2330,13 @@
       <c r="A136" s="1">
         <v>14499</v>
       </c>
-      <c r="B136" s="2">
+      <c r="B136">
         <v>2007</v>
       </c>
-      <c r="C136" s="2">
+      <c r="C136">
         <v>170</v>
       </c>
-      <c r="D136" s="2">
+      <c r="D136">
         <v>125000</v>
       </c>
     </row>
@@ -2345,13 +2344,13 @@
       <c r="A137" s="1">
         <v>1450</v>
       </c>
-      <c r="B137" s="2">
+      <c r="B137">
         <v>1992</v>
       </c>
-      <c r="C137" s="2">
+      <c r="C137">
         <v>136</v>
       </c>
-      <c r="D137" s="2">
+      <c r="D137">
         <v>150000</v>
       </c>
     </row>
@@ -2359,13 +2358,13 @@
       <c r="A138" s="1">
         <v>4300</v>
       </c>
-      <c r="B138" s="2">
+      <c r="B138">
         <v>2005</v>
       </c>
-      <c r="C138" s="2">
+      <c r="C138">
         <v>90</v>
       </c>
-      <c r="D138" s="2">
+      <c r="D138">
         <v>150000</v>
       </c>
     </row>
@@ -2373,13 +2372,13 @@
       <c r="A139" s="1">
         <v>2499</v>
       </c>
-      <c r="B139" s="2">
+      <c r="B139">
         <v>2003</v>
       </c>
-      <c r="C139" s="2">
+      <c r="C139">
         <v>110</v>
       </c>
-      <c r="D139" s="2">
+      <c r="D139">
         <v>150000</v>
       </c>
     </row>
@@ -2387,13 +2386,13 @@
       <c r="A140" s="1">
         <v>3450</v>
       </c>
-      <c r="B140" s="2">
+      <c r="B140">
         <v>2007</v>
       </c>
-      <c r="C140" s="2">
+      <c r="C140">
         <v>120</v>
       </c>
-      <c r="D140" s="2">
+      <c r="D140">
         <v>150000</v>
       </c>
     </row>
@@ -2401,13 +2400,13 @@
       <c r="A141" s="1">
         <v>350</v>
       </c>
-      <c r="B141" s="2">
+      <c r="B141">
         <v>1996</v>
       </c>
-      <c r="C141" s="2">
+      <c r="C141">
         <v>122</v>
       </c>
-      <c r="D141" s="2">
+      <c r="D141">
         <v>150000</v>
       </c>
     </row>
@@ -2415,13 +2414,13 @@
       <c r="A142" s="1">
         <v>3550</v>
       </c>
-      <c r="B142" s="2">
+      <c r="B142">
         <v>2000</v>
       </c>
-      <c r="C142" s="2">
+      <c r="C142">
         <v>184</v>
       </c>
-      <c r="D142" s="2">
+      <c r="D142">
         <v>150000</v>
       </c>
     </row>
@@ -2429,13 +2428,13 @@
       <c r="A143" s="1">
         <v>8250</v>
       </c>
-      <c r="B143" s="2">
+      <c r="B143">
         <v>2010</v>
       </c>
-      <c r="C143" s="2">
+      <c r="C143">
         <v>109</v>
       </c>
-      <c r="D143" s="2">
+      <c r="D143">
         <v>125000</v>
       </c>
     </row>
@@ -2443,13 +2442,13 @@
       <c r="A144" s="1">
         <v>800</v>
       </c>
-      <c r="B144" s="2">
+      <c r="B144">
         <v>1998</v>
       </c>
-      <c r="C144" s="2">
+      <c r="C144">
         <v>54</v>
       </c>
-      <c r="D144" s="2">
+      <c r="D144">
         <v>150000</v>
       </c>
     </row>
@@ -2457,13 +2456,13 @@
       <c r="A145" s="1">
         <v>1500</v>
       </c>
-      <c r="B145" s="2">
+      <c r="B145">
         <v>1996</v>
       </c>
-      <c r="C145" s="2">
+      <c r="C145">
         <v>126</v>
       </c>
-      <c r="D145" s="2">
+      <c r="D145">
         <v>150000</v>
       </c>
     </row>
@@ -2471,13 +2470,13 @@
       <c r="A146" s="1">
         <v>4200</v>
       </c>
-      <c r="B146" s="2">
+      <c r="B146">
         <v>2003</v>
       </c>
-      <c r="C146" s="2">
+      <c r="C146">
         <v>204</v>
       </c>
-      <c r="D146" s="2">
+      <c r="D146">
         <v>150000</v>
       </c>
     </row>
@@ -2485,13 +2484,13 @@
       <c r="A147" s="1">
         <v>150</v>
       </c>
-      <c r="B147" s="2">
+      <c r="B147">
         <v>1985</v>
       </c>
-      <c r="C147" s="2">
+      <c r="C147">
         <v>0</v>
       </c>
-      <c r="D147" s="2">
+      <c r="D147">
         <v>150000</v>
       </c>
     </row>
@@ -2499,13 +2498,13 @@
       <c r="A148" s="1">
         <v>1000</v>
       </c>
-      <c r="B148" s="2">
+      <c r="B148">
         <v>1996</v>
       </c>
-      <c r="C148" s="2">
+      <c r="C148">
         <v>75</v>
       </c>
-      <c r="D148" s="2">
+      <c r="D148">
         <v>150000</v>
       </c>
     </row>
@@ -2513,13 +2512,13 @@
       <c r="A149" s="1">
         <v>300</v>
       </c>
-      <c r="B149" s="2">
+      <c r="B149">
         <v>2005</v>
       </c>
-      <c r="C149" s="2">
+      <c r="C149">
         <v>0</v>
       </c>
-      <c r="D149" s="2">
+      <c r="D149">
         <v>40000</v>
       </c>
     </row>
@@ -2527,13 +2526,13 @@
       <c r="A150" s="1">
         <v>800</v>
       </c>
-      <c r="B150" s="2">
+      <c r="B150">
         <v>2004</v>
       </c>
-      <c r="C150" s="2">
+      <c r="C150">
         <v>88</v>
       </c>
-      <c r="D150" s="2">
+      <c r="D150">
         <v>150000</v>
       </c>
     </row>
@@ -2541,13 +2540,13 @@
       <c r="A151" s="1">
         <v>2300</v>
       </c>
-      <c r="B151" s="2">
+      <c r="B151">
         <v>2000</v>
       </c>
-      <c r="C151" s="2">
+      <c r="C151">
         <v>160</v>
       </c>
-      <c r="D151" s="2">
+      <c r="D151">
         <v>150000</v>
       </c>
     </row>
@@ -2555,13 +2554,13 @@
       <c r="A152" s="1">
         <v>4000</v>
       </c>
-      <c r="B152" s="2">
+      <c r="B152">
         <v>2003</v>
       </c>
-      <c r="C152" s="2">
+      <c r="C152">
         <v>163</v>
       </c>
-      <c r="D152" s="2">
+      <c r="D152">
         <v>150000</v>
       </c>
     </row>
@@ -2569,13 +2568,13 @@
       <c r="A153" s="1">
         <v>6799</v>
       </c>
-      <c r="B153" s="2">
+      <c r="B153">
         <v>2009</v>
       </c>
-      <c r="C153" s="2">
+      <c r="C153">
         <v>60</v>
       </c>
-      <c r="D153" s="2">
+      <c r="D153">
         <v>20000</v>
       </c>
     </row>
@@ -2583,13 +2582,13 @@
       <c r="A154" s="1">
         <v>0</v>
       </c>
-      <c r="B154" s="2">
+      <c r="B154">
         <v>2004</v>
       </c>
-      <c r="C154" s="2">
+      <c r="C154">
         <v>101</v>
       </c>
-      <c r="D154" s="2">
+      <c r="D154">
         <v>150000</v>
       </c>
     </row>
@@ -2597,13 +2596,13 @@
       <c r="A155" s="1">
         <v>9450</v>
       </c>
-      <c r="B155" s="2">
+      <c r="B155">
         <v>2004</v>
       </c>
-      <c r="C155" s="2">
+      <c r="C155">
         <v>170</v>
       </c>
-      <c r="D155" s="2">
+      <c r="D155">
         <v>150000</v>
       </c>
     </row>
@@ -2611,13 +2610,13 @@
       <c r="A156" s="1">
         <v>0</v>
       </c>
-      <c r="B156" s="2">
+      <c r="B156">
         <v>2006</v>
       </c>
-      <c r="C156" s="2">
+      <c r="C156">
         <v>0</v>
       </c>
-      <c r="D156" s="2">
+      <c r="D156">
         <v>5000</v>
       </c>
     </row>
@@ -2625,13 +2624,13 @@
       <c r="A157" s="1">
         <v>14500</v>
       </c>
-      <c r="B157" s="2">
+      <c r="B157">
         <v>2017</v>
       </c>
-      <c r="C157" s="2">
+      <c r="C157">
         <v>136</v>
       </c>
-      <c r="D157" s="2">
+      <c r="D157">
         <v>125000</v>
       </c>
     </row>
@@ -2639,13 +2638,13 @@
       <c r="A158" s="1">
         <v>6890</v>
       </c>
-      <c r="B158" s="2">
+      <c r="B158">
         <v>2003</v>
       </c>
-      <c r="C158" s="2">
+      <c r="C158">
         <v>170</v>
       </c>
-      <c r="D158" s="2">
+      <c r="D158">
         <v>125000</v>
       </c>
     </row>
@@ -2653,13 +2652,13 @@
       <c r="A159" s="1">
         <v>7500</v>
       </c>
-      <c r="B159" s="2">
+      <c r="B159">
         <v>2007</v>
       </c>
-      <c r="C159" s="2">
+      <c r="C159">
         <v>194</v>
       </c>
-      <c r="D159" s="2">
+      <c r="D159">
         <v>5000</v>
       </c>
     </row>
@@ -2667,13 +2666,13 @@
       <c r="A160" s="1">
         <v>800</v>
       </c>
-      <c r="B160" s="2">
+      <c r="B160">
         <v>1993</v>
       </c>
-      <c r="C160" s="2">
+      <c r="C160">
         <v>0</v>
       </c>
-      <c r="D160" s="2">
+      <c r="D160">
         <v>10000</v>
       </c>
     </row>
@@ -2681,13 +2680,13 @@
       <c r="A161" s="1">
         <v>1499</v>
       </c>
-      <c r="B161" s="2">
+      <c r="B161">
         <v>2002</v>
       </c>
-      <c r="C161" s="2">
+      <c r="C161">
         <v>140</v>
       </c>
-      <c r="D161" s="2">
+      <c r="D161">
         <v>150000</v>
       </c>
     </row>
@@ -2695,13 +2694,13 @@
       <c r="A162" s="1">
         <v>500</v>
       </c>
-      <c r="B162" s="2">
+      <c r="B162">
         <v>1999</v>
       </c>
-      <c r="C162" s="2">
+      <c r="C162">
         <v>0</v>
       </c>
-      <c r="D162" s="2">
+      <c r="D162">
         <v>150000</v>
       </c>
     </row>
@@ -2709,13 +2708,13 @@
       <c r="A163" s="1">
         <v>1495</v>
       </c>
-      <c r="B163" s="2">
+      <c r="B163">
         <v>2001</v>
       </c>
-      <c r="C163" s="2">
+      <c r="C163">
         <v>64</v>
       </c>
-      <c r="D163" s="2">
+      <c r="D163">
         <v>150000</v>
       </c>
     </row>
@@ -2723,13 +2722,13 @@
       <c r="A164" s="1">
         <v>300</v>
       </c>
-      <c r="B164" s="2">
+      <c r="B164">
         <v>1994</v>
       </c>
-      <c r="C164" s="2">
+      <c r="C164">
         <v>0</v>
       </c>
-      <c r="D164" s="2">
+      <c r="D164">
         <v>150000</v>
       </c>
     </row>
@@ -2737,13 +2736,13 @@
       <c r="A165" s="1">
         <v>1200</v>
       </c>
-      <c r="B165" s="2">
+      <c r="B165">
         <v>2018</v>
       </c>
-      <c r="C165" s="2">
+      <c r="C165">
         <v>75</v>
       </c>
-      <c r="D165" s="2">
+      <c r="D165">
         <v>150000</v>
       </c>
     </row>
@@ -2751,13 +2750,13 @@
       <c r="A166" s="1">
         <v>850</v>
       </c>
-      <c r="B166" s="2">
+      <c r="B166">
         <v>1989</v>
       </c>
-      <c r="C166" s="2">
+      <c r="C166">
         <v>69</v>
       </c>
-      <c r="D166" s="2">
+      <c r="D166">
         <v>125000</v>
       </c>
     </row>
@@ -2765,13 +2764,13 @@
       <c r="A167" s="1">
         <v>8500</v>
       </c>
-      <c r="B167" s="2">
+      <c r="B167">
         <v>2007</v>
       </c>
-      <c r="C167" s="2">
+      <c r="C167">
         <v>131</v>
       </c>
-      <c r="D167" s="2">
+      <c r="D167">
         <v>150000</v>
       </c>
     </row>
@@ -2779,13 +2778,13 @@
       <c r="A168" s="1">
         <v>300</v>
       </c>
-      <c r="B168" s="2">
+      <c r="B168">
         <v>1998</v>
       </c>
-      <c r="C168" s="2">
+      <c r="C168">
         <v>0</v>
       </c>
-      <c r="D168" s="2">
+      <c r="D168">
         <v>150000</v>
       </c>
     </row>
@@ -2793,13 +2792,13 @@
       <c r="A169" s="1">
         <v>1500</v>
       </c>
-      <c r="B169" s="2">
+      <c r="B169">
         <v>2000</v>
       </c>
-      <c r="C169" s="2">
+      <c r="C169">
         <v>75</v>
       </c>
-      <c r="D169" s="2">
+      <c r="D169">
         <v>125000</v>
       </c>
     </row>
@@ -2807,13 +2806,13 @@
       <c r="A170" s="1">
         <v>950</v>
       </c>
-      <c r="B170" s="2">
+      <c r="B170">
         <v>1995</v>
       </c>
-      <c r="C170" s="2">
+      <c r="C170">
         <v>115</v>
       </c>
-      <c r="D170" s="2">
+      <c r="D170">
         <v>150000</v>
       </c>
     </row>
@@ -2821,13 +2820,13 @@
       <c r="A171" s="1">
         <v>3200</v>
       </c>
-      <c r="B171" s="2">
+      <c r="B171">
         <v>2004</v>
       </c>
-      <c r="C171" s="2">
+      <c r="C171">
         <v>64</v>
       </c>
-      <c r="D171" s="2">
+      <c r="D171">
         <v>80000</v>
       </c>
     </row>
@@ -2835,13 +2834,13 @@
       <c r="A172" s="1">
         <v>11890</v>
       </c>
-      <c r="B172" s="2">
+      <c r="B172">
         <v>2011</v>
       </c>
-      <c r="C172" s="2">
+      <c r="C172">
         <v>116</v>
       </c>
-      <c r="D172" s="2">
+      <c r="D172">
         <v>150000</v>
       </c>
     </row>
@@ -2849,13 +2848,13 @@
       <c r="A173" s="1">
         <v>2900</v>
       </c>
-      <c r="B173" s="2">
+      <c r="B173">
         <v>2000</v>
       </c>
-      <c r="C173" s="2">
+      <c r="C173">
         <v>170</v>
       </c>
-      <c r="D173" s="2">
+      <c r="D173">
         <v>150000</v>
       </c>
     </row>
@@ -2863,13 +2862,13 @@
       <c r="A174" s="1">
         <v>19750</v>
       </c>
-      <c r="B174" s="2">
+      <c r="B174">
         <v>2006</v>
       </c>
-      <c r="C174" s="2">
+      <c r="C174">
         <v>305</v>
       </c>
-      <c r="D174" s="2">
+      <c r="D174">
         <v>50000</v>
       </c>
     </row>
@@ -2877,13 +2876,13 @@
       <c r="A175" s="1">
         <v>9800</v>
       </c>
-      <c r="B175" s="2">
+      <c r="B175">
         <v>2006</v>
       </c>
-      <c r="C175" s="2">
+      <c r="C175">
         <v>150</v>
       </c>
-      <c r="D175" s="2">
+      <c r="D175">
         <v>60000</v>
       </c>
     </row>
@@ -2891,13 +2890,13 @@
       <c r="A176" s="1">
         <v>1990</v>
       </c>
-      <c r="B176" s="2">
+      <c r="B176">
         <v>2003</v>
       </c>
-      <c r="C176" s="2">
+      <c r="C176">
         <v>80</v>
       </c>
-      <c r="D176" s="2">
+      <c r="D176">
         <v>125000</v>
       </c>
     </row>
@@ -2905,13 +2904,13 @@
       <c r="A177" s="1">
         <v>10500</v>
       </c>
-      <c r="B177" s="2">
+      <c r="B177">
         <v>2006</v>
       </c>
-      <c r="C177" s="2">
+      <c r="C177">
         <v>150</v>
       </c>
-      <c r="D177" s="2">
+      <c r="D177">
         <v>150000</v>
       </c>
     </row>
@@ -2919,13 +2918,13 @@
       <c r="A178" s="1">
         <v>11000</v>
       </c>
-      <c r="B178" s="2">
+      <c r="B178">
         <v>2012</v>
       </c>
-      <c r="C178" s="2">
+      <c r="C178">
         <v>131</v>
       </c>
-      <c r="D178" s="2">
+      <c r="D178">
         <v>70000</v>
       </c>
     </row>
@@ -2933,13 +2932,13 @@
       <c r="A179" s="1">
         <v>300</v>
       </c>
-      <c r="B179" s="2">
+      <c r="B179">
         <v>1997</v>
       </c>
-      <c r="C179" s="2">
+      <c r="C179">
         <v>0</v>
       </c>
-      <c r="D179" s="2">
+      <c r="D179">
         <v>150000</v>
       </c>
     </row>
@@ -2947,13 +2946,13 @@
       <c r="A180" s="1">
         <v>2390</v>
       </c>
-      <c r="B180" s="2">
+      <c r="B180">
         <v>2000</v>
       </c>
-      <c r="C180" s="2">
+      <c r="C180">
         <v>197</v>
       </c>
-      <c r="D180" s="2">
+      <c r="D180">
         <v>150000</v>
       </c>
     </row>
@@ -2961,13 +2960,13 @@
       <c r="A181" s="1">
         <v>16449</v>
       </c>
-      <c r="B181" s="2">
+      <c r="B181">
         <v>2015</v>
       </c>
-      <c r="C181" s="2">
+      <c r="C181">
         <v>110</v>
       </c>
-      <c r="D181" s="2">
+      <c r="D181">
         <v>10000</v>
       </c>
     </row>
@@ -2975,13 +2974,13 @@
       <c r="A182" s="1">
         <v>2999</v>
       </c>
-      <c r="B182" s="2">
+      <c r="B182">
         <v>2001</v>
       </c>
-      <c r="C182" s="2">
+      <c r="C182">
         <v>0</v>
       </c>
-      <c r="D182" s="2">
+      <c r="D182">
         <v>150000</v>
       </c>
     </row>
@@ -2989,13 +2988,13 @@
       <c r="A183" s="1">
         <v>3000</v>
       </c>
-      <c r="B183" s="2">
+      <c r="B183">
         <v>2016</v>
       </c>
-      <c r="C183" s="2">
+      <c r="C183">
         <v>75</v>
       </c>
-      <c r="D183" s="2">
+      <c r="D183">
         <v>150000</v>
       </c>
     </row>
@@ -3003,13 +3002,13 @@
       <c r="A184" s="1">
         <v>14300</v>
       </c>
-      <c r="B184" s="2">
+      <c r="B184">
         <v>2011</v>
       </c>
-      <c r="C184" s="2">
+      <c r="C184">
         <v>120</v>
       </c>
-      <c r="D184" s="2">
+      <c r="D184">
         <v>60000</v>
       </c>
     </row>
@@ -3017,13 +3016,13 @@
       <c r="A185" s="1">
         <v>5999</v>
       </c>
-      <c r="B185" s="2">
+      <c r="B185">
         <v>2009</v>
       </c>
-      <c r="C185" s="2">
+      <c r="C185">
         <v>80</v>
       </c>
-      <c r="D185" s="2">
+      <c r="D185">
         <v>125000</v>
       </c>
     </row>
@@ -3031,13 +3030,13 @@
       <c r="A186" s="1">
         <v>3700</v>
       </c>
-      <c r="B186" s="2">
+      <c r="B186">
         <v>2003</v>
       </c>
-      <c r="C186" s="2">
+      <c r="C186">
         <v>179</v>
       </c>
-      <c r="D186" s="2">
+      <c r="D186">
         <v>150000</v>
       </c>
     </row>
@@ -3045,13 +3044,13 @@
       <c r="A187" s="1">
         <v>8999</v>
       </c>
-      <c r="B187" s="2">
+      <c r="B187">
         <v>2007</v>
       </c>
-      <c r="C187" s="2">
+      <c r="C187">
         <v>105</v>
       </c>
-      <c r="D187" s="2">
+      <c r="D187">
         <v>90000</v>
       </c>
     </row>
@@ -3059,13 +3058,13 @@
       <c r="A188" s="1">
         <v>14000</v>
       </c>
-      <c r="B188" s="2">
+      <c r="B188">
         <v>2008</v>
       </c>
-      <c r="C188" s="2">
+      <c r="C188">
         <v>235</v>
       </c>
-      <c r="D188" s="2">
+      <c r="D188">
         <v>150000</v>
       </c>
     </row>
@@ -3073,13 +3072,13 @@
       <c r="A189" s="1">
         <v>2790</v>
       </c>
-      <c r="B189" s="2">
+      <c r="B189">
         <v>1992</v>
       </c>
-      <c r="C189" s="2">
+      <c r="C189">
         <v>90</v>
       </c>
-      <c r="D189" s="2">
+      <c r="D189">
         <v>80000</v>
       </c>
     </row>
@@ -3087,13 +3086,13 @@
       <c r="A190" s="1">
         <v>13400</v>
       </c>
-      <c r="B190" s="2">
+      <c r="B190">
         <v>2008</v>
       </c>
-      <c r="C190" s="2">
+      <c r="C190">
         <v>170</v>
       </c>
-      <c r="D190" s="2">
+      <c r="D190">
         <v>100000</v>
       </c>
     </row>
@@ -3101,13 +3100,13 @@
       <c r="A191" s="1">
         <v>4900</v>
       </c>
-      <c r="B191" s="2">
+      <c r="B191">
         <v>2006</v>
       </c>
-      <c r="C191" s="2">
+      <c r="C191">
         <v>102</v>
       </c>
-      <c r="D191" s="2">
+      <c r="D191">
         <v>150000</v>
       </c>
     </row>
@@ -3115,13 +3114,13 @@
       <c r="A192" s="1">
         <v>11299</v>
       </c>
-      <c r="B192" s="2">
+      <c r="B192">
         <v>2006</v>
       </c>
-      <c r="C192" s="2">
+      <c r="C192">
         <v>250</v>
       </c>
-      <c r="D192" s="2">
+      <c r="D192">
         <v>150000</v>
       </c>
     </row>
@@ -3129,13 +3128,13 @@
       <c r="A193" s="1">
         <v>550</v>
       </c>
-      <c r="B193" s="2">
+      <c r="B193">
         <v>1997</v>
       </c>
-      <c r="C193" s="2">
+      <c r="C193">
         <v>75</v>
       </c>
-      <c r="D193" s="2">
+      <c r="D193">
         <v>150000</v>
       </c>
     </row>
@@ -3143,13 +3142,13 @@
       <c r="A194" s="1">
         <v>1400</v>
       </c>
-      <c r="B194" s="2">
+      <c r="B194">
         <v>2006</v>
       </c>
-      <c r="C194" s="2">
+      <c r="C194">
         <v>88</v>
       </c>
-      <c r="D194" s="2">
+      <c r="D194">
         <v>150000</v>
       </c>
     </row>
@@ -3157,13 +3156,13 @@
       <c r="A195" s="1">
         <v>1200</v>
       </c>
-      <c r="B195" s="2">
+      <c r="B195">
         <v>1990</v>
       </c>
-      <c r="C195" s="2">
+      <c r="C195">
         <v>45</v>
       </c>
-      <c r="D195" s="2">
+      <c r="D195">
         <v>150000</v>
       </c>
     </row>
@@ -3171,13 +3170,13 @@
       <c r="A196" s="1">
         <v>9500</v>
       </c>
-      <c r="B196" s="2">
+      <c r="B196">
         <v>2011</v>
       </c>
-      <c r="C196" s="2">
+      <c r="C196">
         <v>131</v>
       </c>
-      <c r="D196" s="2">
+      <c r="D196">
         <v>150000</v>
       </c>
     </row>
@@ -3185,13 +3184,13 @@
       <c r="A197" s="1">
         <v>1800</v>
       </c>
-      <c r="B197" s="2">
+      <c r="B197">
         <v>1999</v>
       </c>
-      <c r="C197" s="2">
+      <c r="C197">
         <v>90</v>
       </c>
-      <c r="D197" s="2">
+      <c r="D197">
         <v>150000</v>
       </c>
     </row>
@@ -3199,13 +3198,13 @@
       <c r="A198" s="1">
         <v>2800</v>
       </c>
-      <c r="B198" s="2">
+      <c r="B198">
         <v>2018</v>
       </c>
-      <c r="C198" s="2">
+      <c r="C198">
         <v>75</v>
       </c>
-      <c r="D198" s="2">
+      <c r="D198">
         <v>125000</v>
       </c>
     </row>
@@ -3213,13 +3212,13 @@
       <c r="A199" s="1">
         <v>3200</v>
       </c>
-      <c r="B199" s="2">
+      <c r="B199">
         <v>2006</v>
       </c>
-      <c r="C199" s="2">
+      <c r="C199">
         <v>0</v>
       </c>
-      <c r="D199" s="2">
+      <c r="D199">
         <v>150000</v>
       </c>
     </row>
@@ -3227,13 +3226,13 @@
       <c r="A200" s="1">
         <v>1350</v>
       </c>
-      <c r="B200" s="2">
+      <c r="B200">
         <v>2002</v>
       </c>
-      <c r="C200" s="2">
+      <c r="C200">
         <v>60</v>
       </c>
-      <c r="D200" s="2">
+      <c r="D200">
         <v>150000</v>
       </c>
     </row>
@@ -3241,13 +3240,13 @@
       <c r="A201" s="1">
         <v>11000</v>
       </c>
-      <c r="B201" s="2">
+      <c r="B201">
         <v>2006</v>
       </c>
-      <c r="C201" s="2">
+      <c r="C201">
         <v>231</v>
       </c>
-      <c r="D201" s="2">
+      <c r="D201">
         <v>150000</v>
       </c>
     </row>
@@ -3255,13 +3254,13 @@
       <c r="A202" s="1">
         <v>1999</v>
       </c>
-      <c r="B202" s="2">
+      <c r="B202">
         <v>2016</v>
       </c>
-      <c r="C202" s="2">
+      <c r="C202">
         <v>110</v>
       </c>
-      <c r="D202" s="2">
+      <c r="D202">
         <v>150000</v>
       </c>
     </row>
@@ -3269,13 +3268,13 @@
       <c r="A203" s="1">
         <v>6900</v>
       </c>
-      <c r="B203" s="2">
+      <c r="B203">
         <v>2006</v>
       </c>
-      <c r="C203" s="2">
+      <c r="C203">
         <v>163</v>
       </c>
-      <c r="D203" s="2">
+      <c r="D203">
         <v>100000</v>
       </c>
     </row>
@@ -3283,13 +3282,13 @@
       <c r="A204" s="1">
         <v>1600</v>
       </c>
-      <c r="B204" s="2">
+      <c r="B204">
         <v>1996</v>
       </c>
-      <c r="C204" s="2">
+      <c r="C204">
         <v>0</v>
       </c>
-      <c r="D204" s="2">
+      <c r="D204">
         <v>150000</v>
       </c>
     </row>
@@ -3297,13 +3296,13 @@
       <c r="A205" s="1">
         <v>12999</v>
       </c>
-      <c r="B205" s="2">
+      <c r="B205">
         <v>2008</v>
       </c>
-      <c r="C205" s="2">
+      <c r="C205">
         <v>179</v>
       </c>
-      <c r="D205" s="2">
+      <c r="D205">
         <v>150000</v>
       </c>
     </row>
@@ -3311,13 +3310,13 @@
       <c r="A206" s="1">
         <v>18400</v>
       </c>
-      <c r="B206" s="2">
+      <c r="B206">
         <v>2011</v>
       </c>
-      <c r="C206" s="2">
+      <c r="C206">
         <v>313</v>
       </c>
-      <c r="D206" s="2">
+      <c r="D206">
         <v>150000</v>
       </c>
     </row>
@@ -3325,13 +3324,13 @@
       <c r="A207" s="1">
         <v>999</v>
       </c>
-      <c r="B207" s="2">
+      <c r="B207">
         <v>1995</v>
       </c>
-      <c r="C207" s="2">
+      <c r="C207">
         <v>75</v>
       </c>
-      <c r="D207" s="2">
+      <c r="D207">
         <v>150000</v>
       </c>
     </row>
@@ -3339,13 +3338,13 @@
       <c r="A208" s="1">
         <v>12899</v>
       </c>
-      <c r="B208" s="2">
+      <c r="B208">
         <v>2009</v>
       </c>
-      <c r="C208" s="2">
+      <c r="C208">
         <v>140</v>
       </c>
-      <c r="D208" s="2">
+      <c r="D208">
         <v>150000</v>
       </c>
     </row>
@@ -3353,13 +3352,13 @@
       <c r="A209" s="1">
         <v>10500</v>
       </c>
-      <c r="B209" s="2">
+      <c r="B209">
         <v>2010</v>
       </c>
-      <c r="C209" s="2">
+      <c r="C209">
         <v>143</v>
       </c>
-      <c r="D209" s="2">
+      <c r="D209">
         <v>150000</v>
       </c>
     </row>
@@ -3367,13 +3366,13 @@
       <c r="A210" s="1">
         <v>2250</v>
       </c>
-      <c r="B210" s="2">
+      <c r="B210">
         <v>2001</v>
       </c>
-      <c r="C210" s="2">
+      <c r="C210">
         <v>41</v>
       </c>
-      <c r="D210" s="2">
+      <c r="D210">
         <v>150000</v>
       </c>
     </row>
@@ -3381,13 +3380,13 @@
       <c r="A211" s="1">
         <v>8500</v>
       </c>
-      <c r="B211" s="2">
+      <c r="B211">
         <v>2010</v>
       </c>
-      <c r="C211" s="2">
+      <c r="C211">
         <v>80</v>
       </c>
-      <c r="D211" s="2">
+      <c r="D211">
         <v>50000</v>
       </c>
     </row>
@@ -3395,13 +3394,13 @@
       <c r="A212" s="1">
         <v>14900</v>
       </c>
-      <c r="B212" s="2">
+      <c r="B212">
         <v>2007</v>
       </c>
-      <c r="C212" s="2">
+      <c r="C212">
         <v>265</v>
       </c>
-      <c r="D212" s="2">
+      <c r="D212">
         <v>150000</v>
       </c>
     </row>
@@ -3409,13 +3408,13 @@
       <c r="A213" s="1">
         <v>500</v>
       </c>
-      <c r="B213" s="2">
+      <c r="B213">
         <v>1994</v>
       </c>
-      <c r="C213" s="2">
+      <c r="C213">
         <v>75</v>
       </c>
-      <c r="D213" s="2">
+      <c r="D213">
         <v>150000</v>
       </c>
     </row>
@@ -3423,13 +3422,13 @@
       <c r="A214" s="1">
         <v>1200</v>
       </c>
-      <c r="B214" s="2">
+      <c r="B214">
         <v>2002</v>
       </c>
-      <c r="C214" s="2">
+      <c r="C214">
         <v>45</v>
       </c>
-      <c r="D214" s="2">
+      <c r="D214">
         <v>150000</v>
       </c>
     </row>
@@ -3437,13 +3436,13 @@
       <c r="A215" s="1">
         <v>1250</v>
       </c>
-      <c r="B215" s="2">
+      <c r="B215">
         <v>1996</v>
       </c>
-      <c r="C215" s="2">
+      <c r="C215">
         <v>125</v>
       </c>
-      <c r="D215" s="2">
+      <c r="D215">
         <v>150000</v>
       </c>
     </row>
@@ -3451,13 +3450,13 @@
       <c r="A216" s="1">
         <v>370</v>
       </c>
-      <c r="B216" s="2">
+      <c r="B216">
         <v>1992</v>
       </c>
-      <c r="C216" s="2">
+      <c r="C216">
         <v>54</v>
       </c>
-      <c r="D216" s="2">
+      <c r="D216">
         <v>125000</v>
       </c>
     </row>
@@ -3465,13 +3464,13 @@
       <c r="A217" s="1">
         <v>1000</v>
       </c>
-      <c r="B217" s="2">
+      <c r="B217">
         <v>1999</v>
       </c>
-      <c r="C217" s="2">
+      <c r="C217">
         <v>165</v>
       </c>
-      <c r="D217" s="2">
+      <c r="D217">
         <v>150000</v>
       </c>
     </row>
@@ -3479,13 +3478,13 @@
       <c r="A218" s="1">
         <v>350</v>
       </c>
-      <c r="B218" s="2">
+      <c r="B218">
         <v>1993</v>
       </c>
-      <c r="C218" s="2">
+      <c r="C218">
         <v>88</v>
       </c>
-      <c r="D218" s="2">
+      <c r="D218">
         <v>150000</v>
       </c>
     </row>
@@ -3493,13 +3492,13 @@
       <c r="A219" s="1">
         <v>8600</v>
       </c>
-      <c r="B219" s="2">
+      <c r="B219">
         <v>2007</v>
       </c>
-      <c r="C219" s="2">
+      <c r="C219">
         <v>197</v>
       </c>
-      <c r="D219" s="2">
+      <c r="D219">
         <v>150000</v>
       </c>
     </row>
@@ -3507,13 +3506,13 @@
       <c r="A220" s="1">
         <v>2100</v>
       </c>
-      <c r="B220" s="2">
+      <c r="B220">
         <v>2017</v>
       </c>
-      <c r="C220" s="2">
+      <c r="C220">
         <v>0</v>
       </c>
-      <c r="D220" s="2">
+      <c r="D220">
         <v>150000</v>
       </c>
     </row>
@@ -3521,13 +3520,13 @@
       <c r="A221" s="1">
         <v>2222</v>
       </c>
-      <c r="B221" s="2">
+      <c r="B221">
         <v>1991</v>
       </c>
-      <c r="C221" s="2">
+      <c r="C221">
         <v>98</v>
       </c>
-      <c r="D221" s="2">
+      <c r="D221">
         <v>150000</v>
       </c>
     </row>
@@ -3535,13 +3534,13 @@
       <c r="A222" s="1">
         <v>850</v>
       </c>
-      <c r="B222" s="2">
+      <c r="B222">
         <v>1985</v>
       </c>
-      <c r="C222" s="2">
+      <c r="C222">
         <v>54</v>
       </c>
-      <c r="D222" s="2">
+      <c r="D222">
         <v>150000</v>
       </c>
     </row>
@@ -3549,13 +3548,13 @@
       <c r="A223" s="1">
         <v>11800</v>
       </c>
-      <c r="B223" s="2">
+      <c r="B223">
         <v>2005</v>
       </c>
-      <c r="C223" s="2">
+      <c r="C223">
         <v>218</v>
       </c>
-      <c r="D223" s="2">
+      <c r="D223">
         <v>150000</v>
       </c>
     </row>
@@ -3563,13 +3562,13 @@
       <c r="A224" s="1">
         <v>4000</v>
       </c>
-      <c r="B224" s="2">
+      <c r="B224">
         <v>2008</v>
       </c>
-      <c r="C224" s="2">
+      <c r="C224">
         <v>115</v>
       </c>
-      <c r="D224" s="2">
+      <c r="D224">
         <v>125000</v>
       </c>
     </row>
@@ -3577,13 +3576,13 @@
       <c r="A225" s="1">
         <v>4650</v>
       </c>
-      <c r="B225" s="2">
+      <c r="B225">
         <v>2005</v>
       </c>
-      <c r="C225" s="2">
+      <c r="C225">
         <v>150</v>
       </c>
-      <c r="D225" s="2">
+      <c r="D225">
         <v>150000</v>
       </c>
     </row>
@@ -3591,13 +3590,13 @@
       <c r="A226" s="1">
         <v>1450</v>
       </c>
-      <c r="B226" s="2">
+      <c r="B226">
         <v>1999</v>
       </c>
-      <c r="C226" s="2">
+      <c r="C226">
         <v>75</v>
       </c>
-      <c r="D226" s="2">
+      <c r="D226">
         <v>150000</v>
       </c>
     </row>
@@ -3605,13 +3604,13 @@
       <c r="A227" s="1">
         <v>900</v>
       </c>
-      <c r="B227" s="2">
+      <c r="B227">
         <v>2017</v>
       </c>
-      <c r="C227" s="2">
+      <c r="C227">
         <v>60</v>
       </c>
-      <c r="D227" s="2">
+      <c r="D227">
         <v>150000</v>
       </c>
     </row>
@@ -3619,13 +3618,13 @@
       <c r="A228" s="1">
         <v>800</v>
       </c>
-      <c r="B228" s="2">
+      <c r="B228">
         <v>2002</v>
       </c>
-      <c r="C228" s="2">
+      <c r="C228">
         <v>115</v>
       </c>
-      <c r="D228" s="2">
+      <c r="D228">
         <v>150000</v>
       </c>
     </row>
@@ -3633,13 +3632,13 @@
       <c r="A229" s="1">
         <v>1600</v>
       </c>
-      <c r="B229" s="2">
+      <c r="B229">
         <v>2000</v>
       </c>
-      <c r="C229" s="2">
+      <c r="C229">
         <v>90</v>
       </c>
-      <c r="D229" s="2">
+      <c r="D229">
         <v>150000</v>
       </c>
     </row>
@@ -3647,13 +3646,13 @@
       <c r="A230" s="1">
         <v>2800</v>
       </c>
-      <c r="B230" s="2">
+      <c r="B230">
         <v>2004</v>
       </c>
-      <c r="C230" s="2">
+      <c r="C230">
         <v>75</v>
       </c>
-      <c r="D230" s="2">
+      <c r="D230">
         <v>100000</v>
       </c>
     </row>
@@ -3661,13 +3660,13 @@
       <c r="A231" s="1">
         <v>5499</v>
       </c>
-      <c r="B231" s="2">
+      <c r="B231">
         <v>2004</v>
       </c>
-      <c r="C231" s="2">
+      <c r="C231">
         <v>122</v>
       </c>
-      <c r="D231" s="2">
+      <c r="D231">
         <v>150000</v>
       </c>
     </row>
@@ -3675,13 +3674,13 @@
       <c r="A232" s="1">
         <v>5500</v>
       </c>
-      <c r="B232" s="2">
+      <c r="B232">
         <v>2000</v>
       </c>
-      <c r="C232" s="2">
+      <c r="C232">
         <v>170</v>
       </c>
-      <c r="D232" s="2">
+      <c r="D232">
         <v>150000</v>
       </c>
     </row>
@@ -3689,13 +3688,13 @@
       <c r="A233" s="1">
         <v>0</v>
       </c>
-      <c r="B233" s="2">
+      <c r="B233">
         <v>2001</v>
       </c>
-      <c r="C233" s="2">
+      <c r="C233">
         <v>115</v>
       </c>
-      <c r="D233" s="2">
+      <c r="D233">
         <v>150000</v>
       </c>
     </row>
@@ -3703,13 +3702,13 @@
       <c r="A234" s="1">
         <v>1000</v>
       </c>
-      <c r="B234" s="2">
+      <c r="B234">
         <v>1982</v>
       </c>
-      <c r="C234" s="2">
+      <c r="C234">
         <v>41</v>
       </c>
-      <c r="D234" s="2">
+      <c r="D234">
         <v>150000</v>
       </c>
     </row>
@@ -3717,13 +3716,13 @@
       <c r="A235" s="1">
         <v>3750</v>
       </c>
-      <c r="B235" s="2">
+      <c r="B235">
         <v>2005</v>
       </c>
-      <c r="C235" s="2">
+      <c r="C235">
         <v>75</v>
       </c>
-      <c r="D235" s="2">
+      <c r="D235">
         <v>150000</v>
       </c>
     </row>
@@ -3731,13 +3730,13 @@
       <c r="A236" s="1">
         <v>1440</v>
       </c>
-      <c r="B236" s="2">
+      <c r="B236">
         <v>2003</v>
       </c>
-      <c r="C236" s="2">
+      <c r="C236">
         <v>109</v>
       </c>
-      <c r="D236" s="2">
+      <c r="D236">
         <v>150000</v>
       </c>
     </row>
@@ -3745,13 +3744,13 @@
       <c r="A237" s="1">
         <v>1150</v>
       </c>
-      <c r="B237" s="2">
+      <c r="B237">
         <v>2000</v>
       </c>
-      <c r="C237" s="2">
+      <c r="C237">
         <v>75</v>
       </c>
-      <c r="D237" s="2">
+      <c r="D237">
         <v>150000</v>
       </c>
     </row>
@@ -3759,13 +3758,13 @@
       <c r="A238" s="1">
         <v>15700</v>
       </c>
-      <c r="B238" s="2">
+      <c r="B238">
         <v>2011</v>
       </c>
-      <c r="C238" s="2">
+      <c r="C238">
         <v>170</v>
       </c>
-      <c r="D238" s="2">
+      <c r="D238">
         <v>90000</v>
       </c>
     </row>
@@ -3773,13 +3772,13 @@
       <c r="A239" s="1">
         <v>899</v>
       </c>
-      <c r="B239" s="2">
+      <c r="B239">
         <v>1995</v>
       </c>
-      <c r="C239" s="2">
+      <c r="C239">
         <v>102</v>
       </c>
-      <c r="D239" s="2">
+      <c r="D239">
         <v>150000</v>
       </c>
     </row>
@@ -3787,13 +3786,13 @@
       <c r="A240" s="1">
         <v>130</v>
       </c>
-      <c r="B240" s="2">
+      <c r="B240">
         <v>1998</v>
       </c>
-      <c r="C240" s="2">
+      <c r="C240">
         <v>0</v>
       </c>
-      <c r="D240" s="2">
+      <c r="D240">
         <v>150000</v>
       </c>
     </row>
@@ -3801,13 +3800,13 @@
       <c r="A241" s="1">
         <v>9200</v>
       </c>
-      <c r="B241" s="2">
+      <c r="B241">
         <v>2006</v>
       </c>
-      <c r="C241" s="2">
+      <c r="C241">
         <v>150</v>
       </c>
-      <c r="D241" s="2">
+      <c r="D241">
         <v>150000</v>
       </c>
     </row>
@@ -3815,13 +3814,13 @@
       <c r="A242" s="1">
         <v>3350</v>
       </c>
-      <c r="B242" s="2">
+      <c r="B242">
         <v>2000</v>
       </c>
-      <c r="C242" s="2">
+      <c r="C242">
         <v>130</v>
       </c>
-      <c r="D242" s="2">
+      <c r="D242">
         <v>150000</v>
       </c>
     </row>
@@ -3829,13 +3828,13 @@
       <c r="A243" s="1">
         <v>2700</v>
       </c>
-      <c r="B243" s="2">
+      <c r="B243">
         <v>2006</v>
       </c>
-      <c r="C243" s="2">
+      <c r="C243">
         <v>75</v>
       </c>
-      <c r="D243" s="2">
+      <c r="D243">
         <v>125000</v>
       </c>
     </row>
@@ -3843,13 +3842,13 @@
       <c r="A244" s="1">
         <v>800</v>
       </c>
-      <c r="B244" s="2">
+      <c r="B244">
         <v>2001</v>
       </c>
-      <c r="C244" s="2">
+      <c r="C244">
         <v>114</v>
       </c>
-      <c r="D244" s="2">
+      <c r="D244">
         <v>150000</v>
       </c>
     </row>
@@ -3857,13 +3856,13 @@
       <c r="A245" s="1">
         <v>10200</v>
       </c>
-      <c r="B245" s="2">
+      <c r="B245">
         <v>2008</v>
       </c>
-      <c r="C245" s="2">
+      <c r="C245">
         <v>0</v>
       </c>
-      <c r="D245" s="2">
+      <c r="D245">
         <v>90000</v>
       </c>
     </row>
@@ -3871,13 +3870,13 @@
       <c r="A246" s="1">
         <v>9800</v>
       </c>
-      <c r="B246" s="2">
+      <c r="B246">
         <v>2008</v>
       </c>
-      <c r="C246" s="2">
+      <c r="C246">
         <v>140</v>
       </c>
-      <c r="D246" s="2">
+      <c r="D246">
         <v>150000</v>
       </c>
     </row>
@@ -3885,13 +3884,13 @@
       <c r="A247" s="1">
         <v>14700</v>
       </c>
-      <c r="B247" s="2">
+      <c r="B247">
         <v>2012</v>
       </c>
-      <c r="C247" s="2">
+      <c r="C247">
         <v>211</v>
       </c>
-      <c r="D247" s="2">
+      <c r="D247">
         <v>60000</v>
       </c>
     </row>
@@ -3899,13 +3898,13 @@
       <c r="A248" s="1">
         <v>1200</v>
       </c>
-      <c r="B248" s="2">
+      <c r="B248">
         <v>1997</v>
       </c>
-      <c r="C248" s="2">
+      <c r="C248">
         <v>101</v>
       </c>
-      <c r="D248" s="2">
+      <c r="D248">
         <v>150000</v>
       </c>
     </row>
@@ -3913,13 +3912,13 @@
       <c r="A249" s="1">
         <v>895</v>
       </c>
-      <c r="B249" s="2">
+      <c r="B249">
         <v>1995</v>
       </c>
-      <c r="C249" s="2">
+      <c r="C249">
         <v>75</v>
       </c>
-      <c r="D249" s="2">
+      <c r="D249">
         <v>70000</v>
       </c>
     </row>
@@ -3927,13 +3926,13 @@
       <c r="A250" s="1">
         <v>950</v>
       </c>
-      <c r="B250" s="2">
+      <c r="B250">
         <v>1995</v>
       </c>
-      <c r="C250" s="2">
+      <c r="C250">
         <v>54</v>
       </c>
-      <c r="D250" s="2">
+      <c r="D250">
         <v>150000</v>
       </c>
     </row>
@@ -3941,13 +3940,13 @@
       <c r="A251" s="1">
         <v>8000</v>
       </c>
-      <c r="B251" s="2">
+      <c r="B251">
         <v>2006</v>
       </c>
-      <c r="C251" s="2">
+      <c r="C251">
         <v>177</v>
       </c>
-      <c r="D251" s="2">
+      <c r="D251">
         <v>150000</v>
       </c>
     </row>
@@ -3955,13 +3954,13 @@
       <c r="A252" s="1">
         <v>6799</v>
       </c>
-      <c r="B252" s="2">
+      <c r="B252">
         <v>2002</v>
       </c>
-      <c r="C252" s="2">
+      <c r="C252">
         <v>286</v>
       </c>
-      <c r="D252" s="2">
+      <c r="D252">
         <v>150000</v>
       </c>
     </row>
@@ -3969,13 +3968,13 @@
       <c r="A253" s="1">
         <v>500</v>
       </c>
-      <c r="B253" s="2">
+      <c r="B253">
         <v>1999</v>
       </c>
-      <c r="C253" s="2">
+      <c r="C253">
         <v>56</v>
       </c>
-      <c r="D253" s="2">
+      <c r="D253">
         <v>150000</v>
       </c>
     </row>
@@ -3983,13 +3982,13 @@
       <c r="A254" s="1">
         <v>11919</v>
       </c>
-      <c r="B254" s="2">
+      <c r="B254">
         <v>2012</v>
       </c>
-      <c r="C254" s="2">
+      <c r="C254">
         <v>90</v>
       </c>
-      <c r="D254" s="2">
+      <c r="D254">
         <v>30000</v>
       </c>
     </row>
@@ -3997,13 +3996,13 @@
       <c r="A255" s="1">
         <v>300</v>
       </c>
-      <c r="B255" s="2">
+      <c r="B255">
         <v>1993</v>
       </c>
-      <c r="C255" s="2">
+      <c r="C255">
         <v>90</v>
       </c>
-      <c r="D255" s="2">
+      <c r="D255">
         <v>150000</v>
       </c>
     </row>
@@ -4011,13 +4010,13 @@
       <c r="A256" s="1">
         <v>10800</v>
       </c>
-      <c r="B256" s="2">
+      <c r="B256">
         <v>2010</v>
       </c>
-      <c r="C256" s="2">
+      <c r="C256">
         <v>105</v>
       </c>
-      <c r="D256" s="2">
+      <c r="D256">
         <v>125000</v>
       </c>
     </row>
@@ -4025,13 +4024,13 @@
       <c r="A257" s="1">
         <v>650</v>
       </c>
-      <c r="B257" s="2">
+      <c r="B257">
         <v>2002</v>
       </c>
-      <c r="C257" s="2">
+      <c r="C257">
         <v>101</v>
       </c>
-      <c r="D257" s="2">
+      <c r="D257">
         <v>150000</v>
       </c>
     </row>
@@ -4039,13 +4038,13 @@
       <c r="A258" s="1">
         <v>800</v>
       </c>
-      <c r="B258" s="2">
+      <c r="B258">
         <v>2000</v>
       </c>
-      <c r="C258" s="2">
+      <c r="C258">
         <v>118</v>
       </c>
-      <c r="D258" s="2">
+      <c r="D258">
         <v>150000</v>
       </c>
     </row>
@@ -4053,13 +4052,13 @@
       <c r="A259" s="1">
         <v>1690</v>
       </c>
-      <c r="B259" s="2">
+      <c r="B259">
         <v>2001</v>
       </c>
-      <c r="C259" s="2">
+      <c r="C259">
         <v>75</v>
       </c>
-      <c r="D259" s="2">
+      <c r="D259">
         <v>150000</v>
       </c>
     </row>
@@ -4067,13 +4066,13 @@
       <c r="A260" s="1">
         <v>3650</v>
       </c>
-      <c r="B260" s="2">
+      <c r="B260">
         <v>2004</v>
       </c>
-      <c r="C260" s="2">
+      <c r="C260">
         <v>113</v>
       </c>
-      <c r="D260" s="2">
+      <c r="D260">
         <v>150000</v>
       </c>
     </row>
@@ -4081,13 +4080,13 @@
       <c r="A261" s="1">
         <v>4850</v>
       </c>
-      <c r="B261" s="2">
+      <c r="B261">
         <v>2009</v>
       </c>
-      <c r="C261" s="2">
+      <c r="C261">
         <v>75</v>
       </c>
-      <c r="D261" s="2">
+      <c r="D261">
         <v>80000</v>
       </c>
     </row>
@@ -4095,13 +4094,13 @@
       <c r="A262" s="1">
         <v>450</v>
       </c>
-      <c r="B262" s="2">
+      <c r="B262">
         <v>2016</v>
       </c>
-      <c r="C262" s="2">
+      <c r="C262">
         <v>0</v>
       </c>
-      <c r="D262" s="2">
+      <c r="D262">
         <v>150000</v>
       </c>
     </row>
@@ -4109,13 +4108,13 @@
       <c r="A263" s="1">
         <v>1450</v>
       </c>
-      <c r="B263" s="2">
+      <c r="B263">
         <v>1999</v>
       </c>
-      <c r="C263" s="2">
+      <c r="C263">
         <v>0</v>
       </c>
-      <c r="D263" s="2">
+      <c r="D263">
         <v>5000</v>
       </c>
     </row>
@@ -4123,13 +4122,13 @@
       <c r="A264" s="1">
         <v>4500</v>
       </c>
-      <c r="B264" s="2">
+      <c r="B264">
         <v>2007</v>
       </c>
-      <c r="C264" s="2">
+      <c r="C264">
         <v>140</v>
       </c>
-      <c r="D264" s="2">
+      <c r="D264">
         <v>150000</v>
       </c>
     </row>
@@ -4137,13 +4136,13 @@
       <c r="A265" s="1">
         <v>3900</v>
       </c>
-      <c r="B265" s="2">
+      <c r="B265">
         <v>2003</v>
       </c>
-      <c r="C265" s="2">
+      <c r="C265">
         <v>131</v>
       </c>
-      <c r="D265" s="2">
+      <c r="D265">
         <v>150000</v>
       </c>
     </row>
@@ -4151,13 +4150,13 @@
       <c r="A266" s="1">
         <v>750</v>
       </c>
-      <c r="B266" s="2">
+      <c r="B266">
         <v>2000</v>
       </c>
-      <c r="C266" s="2">
+      <c r="C266">
         <v>101</v>
       </c>
-      <c r="D266" s="2">
+      <c r="D266">
         <v>150000</v>
       </c>
     </row>
@@ -4165,13 +4164,13 @@
       <c r="A267" s="1">
         <v>5900</v>
       </c>
-      <c r="B267" s="2">
+      <c r="B267">
         <v>1999</v>
       </c>
-      <c r="C267" s="2">
+      <c r="C267">
         <v>184</v>
       </c>
-      <c r="D267" s="2">
+      <c r="D267">
         <v>150000</v>
       </c>
     </row>
@@ -4179,13 +4178,13 @@
       <c r="A268" s="1">
         <v>1100</v>
       </c>
-      <c r="B268" s="2">
+      <c r="B268">
         <v>2000</v>
       </c>
-      <c r="C268" s="2">
+      <c r="C268">
         <v>116</v>
       </c>
-      <c r="D268" s="2">
+      <c r="D268">
         <v>150000</v>
       </c>
     </row>
@@ -4193,13 +4192,13 @@
       <c r="A269" s="1">
         <v>8400</v>
       </c>
-      <c r="B269" s="2">
+      <c r="B269">
         <v>2009</v>
       </c>
-      <c r="C269" s="2">
+      <c r="C269">
         <v>201</v>
       </c>
-      <c r="D269" s="2">
+      <c r="D269">
         <v>70000</v>
       </c>
     </row>
@@ -4207,13 +4206,13 @@
       <c r="A270" s="1">
         <v>1</v>
       </c>
-      <c r="B270" s="2">
+      <c r="B270">
         <v>1990</v>
       </c>
-      <c r="C270" s="2">
+      <c r="C270">
         <v>90</v>
       </c>
-      <c r="D270" s="2">
+      <c r="D270">
         <v>70000</v>
       </c>
     </row>
@@ -4221,13 +4220,13 @@
       <c r="A271" s="1">
         <v>800</v>
       </c>
-      <c r="B271" s="2">
+      <c r="B271">
         <v>1998</v>
       </c>
-      <c r="C271" s="2">
+      <c r="C271">
         <v>75</v>
       </c>
-      <c r="D271" s="2">
+      <c r="D271">
         <v>150000</v>
       </c>
     </row>
@@ -4235,13 +4234,13 @@
       <c r="A272" s="1">
         <v>14950</v>
       </c>
-      <c r="B272" s="2">
+      <c r="B272">
         <v>2009</v>
       </c>
-      <c r="C272" s="2">
+      <c r="C272">
         <v>140</v>
       </c>
-      <c r="D272" s="2">
+      <c r="D272">
         <v>70000</v>
       </c>
     </row>
@@ -4249,13 +4248,13 @@
       <c r="A273" s="1">
         <v>14900</v>
       </c>
-      <c r="B273" s="2">
+      <c r="B273">
         <v>2004</v>
       </c>
-      <c r="C273" s="2">
+      <c r="C273">
         <v>170</v>
       </c>
-      <c r="D273" s="2">
+      <c r="D273">
         <v>70000</v>
       </c>
     </row>
@@ -4263,13 +4262,13 @@
       <c r="A274" s="1">
         <v>2950</v>
       </c>
-      <c r="B274" s="2">
+      <c r="B274">
         <v>1998</v>
       </c>
-      <c r="C274" s="2">
+      <c r="C274">
         <v>235</v>
       </c>
-      <c r="D274" s="2">
+      <c r="D274">
         <v>150000</v>
       </c>
     </row>
@@ -4277,13 +4276,13 @@
       <c r="A275" s="1">
         <v>1500</v>
       </c>
-      <c r="B275" s="2">
+      <c r="B275">
         <v>1994</v>
       </c>
-      <c r="C275" s="2">
+      <c r="C275">
         <v>116</v>
       </c>
-      <c r="D275" s="2">
+      <c r="D275">
         <v>150000</v>
       </c>
     </row>
@@ -4291,13 +4290,13 @@
       <c r="A276" s="1">
         <v>12000</v>
       </c>
-      <c r="B276" s="2">
+      <c r="B276">
         <v>2011</v>
       </c>
-      <c r="C276" s="2">
+      <c r="C276">
         <v>101</v>
       </c>
-      <c r="D276" s="2">
+      <c r="D276">
         <v>150000</v>
       </c>
     </row>
@@ -4305,13 +4304,13 @@
       <c r="A277" s="1">
         <v>2500</v>
       </c>
-      <c r="B277" s="2">
+      <c r="B277">
         <v>2001</v>
       </c>
-      <c r="C277" s="2">
+      <c r="C277">
         <v>150</v>
       </c>
-      <c r="D277" s="2">
+      <c r="D277">
         <v>150000</v>
       </c>
     </row>
@@ -4319,13 +4318,13 @@
       <c r="A278" s="1">
         <v>2400</v>
       </c>
-      <c r="B278" s="2">
+      <c r="B278">
         <v>2001</v>
       </c>
-      <c r="C278" s="2">
+      <c r="C278">
         <v>115</v>
       </c>
-      <c r="D278" s="2">
+      <c r="D278">
         <v>150000</v>
       </c>
     </row>
@@ -4333,13 +4332,13 @@
       <c r="A279" s="1">
         <v>4600</v>
       </c>
-      <c r="B279" s="2">
+      <c r="B279">
         <v>2017</v>
       </c>
-      <c r="C279" s="2">
+      <c r="C279">
         <v>109</v>
       </c>
-      <c r="D279" s="2">
+      <c r="D279">
         <v>125000</v>
       </c>
     </row>
@@ -4347,13 +4346,13 @@
       <c r="A280" s="1">
         <v>6000</v>
       </c>
-      <c r="B280" s="2">
+      <c r="B280">
         <v>1995</v>
       </c>
-      <c r="C280" s="2">
+      <c r="C280">
         <v>286</v>
       </c>
-      <c r="D280" s="2">
+      <c r="D280">
         <v>150000</v>
       </c>
     </row>
@@ -4361,13 +4360,13 @@
       <c r="A281" s="1">
         <v>8950</v>
       </c>
-      <c r="B281" s="2">
+      <c r="B281">
         <v>2012</v>
       </c>
-      <c r="C281" s="2">
+      <c r="C281">
         <v>95</v>
       </c>
-      <c r="D281" s="2">
+      <c r="D281">
         <v>60000</v>
       </c>
     </row>
@@ -4375,13 +4374,13 @@
       <c r="A282" s="1">
         <v>590</v>
       </c>
-      <c r="B282" s="2">
+      <c r="B282">
         <v>1996</v>
       </c>
-      <c r="C282" s="2">
+      <c r="C282">
         <v>0</v>
       </c>
-      <c r="D282" s="2">
+      <c r="D282">
         <v>150000</v>
       </c>
     </row>
@@ -4389,13 +4388,13 @@
       <c r="A283" s="1">
         <v>150</v>
       </c>
-      <c r="B283" s="2">
+      <c r="B283">
         <v>2016</v>
       </c>
-      <c r="C283" s="2">
+      <c r="C283">
         <v>75</v>
       </c>
-      <c r="D283" s="2">
+      <c r="D283">
         <v>50000</v>
       </c>
     </row>
@@ -4403,13 +4402,13 @@
       <c r="A284" s="1">
         <v>18700</v>
       </c>
-      <c r="B284" s="2">
+      <c r="B284">
         <v>2009</v>
       </c>
-      <c r="C284" s="2">
+      <c r="C284">
         <v>213</v>
       </c>
-      <c r="D284" s="2">
+      <c r="D284">
         <v>80000</v>
       </c>
     </row>
@@ -4417,13 +4416,13 @@
       <c r="A285" s="1">
         <v>9500</v>
       </c>
-      <c r="B285" s="2">
+      <c r="B285">
         <v>2012</v>
       </c>
-      <c r="C285" s="2">
+      <c r="C285">
         <v>69</v>
       </c>
-      <c r="D285" s="2">
+      <c r="D285">
         <v>50000</v>
       </c>
     </row>
@@ -4431,13 +4430,13 @@
       <c r="A286" s="1">
         <v>11550</v>
       </c>
-      <c r="B286" s="2">
+      <c r="B286">
         <v>2009</v>
       </c>
-      <c r="C286" s="2">
+      <c r="C286">
         <v>140</v>
       </c>
-      <c r="D286" s="2">
+      <c r="D286">
         <v>125000</v>
       </c>
     </row>
@@ -4445,13 +4444,13 @@
       <c r="A287" s="1">
         <v>1250</v>
       </c>
-      <c r="B287" s="2">
+      <c r="B287">
         <v>2017</v>
       </c>
-      <c r="C287" s="2">
+      <c r="C287">
         <v>0</v>
       </c>
-      <c r="D287" s="2">
+      <c r="D287">
         <v>150000</v>
       </c>
     </row>
@@ -4459,13 +4458,13 @@
       <c r="A288" s="1">
         <v>2400</v>
       </c>
-      <c r="B288" s="2">
+      <c r="B288">
         <v>1989</v>
       </c>
-      <c r="C288" s="2">
+      <c r="C288">
         <v>102</v>
       </c>
-      <c r="D288" s="2">
+      <c r="D288">
         <v>150000</v>
       </c>
     </row>
@@ -4473,13 +4472,13 @@
       <c r="A289" s="1">
         <v>16150</v>
       </c>
-      <c r="B289" s="2">
+      <c r="B289">
         <v>2011</v>
       </c>
-      <c r="C289" s="2">
+      <c r="C289">
         <v>150</v>
       </c>
-      <c r="D289" s="2">
+      <c r="D289">
         <v>30000</v>
       </c>
     </row>
@@ -4487,13 +4486,13 @@
       <c r="A290" s="1">
         <v>3400</v>
       </c>
-      <c r="B290" s="2">
+      <c r="B290">
         <v>2000</v>
       </c>
-      <c r="C290" s="2">
+      <c r="C290">
         <v>0</v>
       </c>
-      <c r="D290" s="2">
+      <c r="D290">
         <v>150000</v>
       </c>
     </row>
@@ -4501,13 +4500,13 @@
       <c r="A291" s="1">
         <v>3000</v>
       </c>
-      <c r="B291" s="2">
+      <c r="B291">
         <v>2000</v>
       </c>
-      <c r="C291" s="2">
+      <c r="C291">
         <v>179</v>
       </c>
-      <c r="D291" s="2">
+      <c r="D291">
         <v>150000</v>
       </c>
     </row>
@@ -4515,13 +4514,13 @@
       <c r="A292" s="1">
         <v>5500</v>
       </c>
-      <c r="B292" s="2">
+      <c r="B292">
         <v>2004</v>
       </c>
-      <c r="C292" s="2">
+      <c r="C292">
         <v>90</v>
       </c>
-      <c r="D292" s="2">
+      <c r="D292">
         <v>150000</v>
       </c>
     </row>
@@ -4529,13 +4528,13 @@
       <c r="A293" s="1">
         <v>2000</v>
       </c>
-      <c r="B293" s="2">
+      <c r="B293">
         <v>2004</v>
       </c>
-      <c r="C293" s="2">
+      <c r="C293">
         <v>122</v>
       </c>
-      <c r="D293" s="2">
+      <c r="D293">
         <v>5000</v>
       </c>
     </row>
@@ -4543,13 +4542,13 @@
       <c r="A294" s="1">
         <v>300</v>
       </c>
-      <c r="B294" s="2">
+      <c r="B294">
         <v>1998</v>
       </c>
-      <c r="C294" s="2">
+      <c r="C294">
         <v>58</v>
       </c>
-      <c r="D294" s="2">
+      <c r="D294">
         <v>125000</v>
       </c>
     </row>
@@ -4557,13 +4556,13 @@
       <c r="A295" s="1">
         <v>890</v>
       </c>
-      <c r="B295" s="2">
+      <c r="B295">
         <v>2000</v>
       </c>
-      <c r="C295" s="2">
+      <c r="C295">
         <v>107</v>
       </c>
-      <c r="D295" s="2">
+      <c r="D295">
         <v>150000</v>
       </c>
     </row>
@@ -4571,13 +4570,13 @@
       <c r="A296" s="1">
         <v>2390</v>
       </c>
-      <c r="B296" s="2">
+      <c r="B296">
         <v>2016</v>
       </c>
-      <c r="C296" s="2">
+      <c r="C296">
         <v>83</v>
       </c>
-      <c r="D296" s="2">
+      <c r="D296">
         <v>150000</v>
       </c>
     </row>
@@ -4585,13 +4584,13 @@
       <c r="A297" s="1">
         <v>1450</v>
       </c>
-      <c r="B297" s="2">
+      <c r="B297">
         <v>2017</v>
       </c>
-      <c r="C297" s="2">
+      <c r="C297">
         <v>0</v>
       </c>
-      <c r="D297" s="2">
+      <c r="D297">
         <v>150000</v>
       </c>
     </row>
@@ -4599,13 +4598,13 @@
       <c r="A298" s="1">
         <v>1699</v>
       </c>
-      <c r="B298" s="2">
+      <c r="B298">
         <v>1999</v>
       </c>
-      <c r="C298" s="2">
+      <c r="C298">
         <v>75</v>
       </c>
-      <c r="D298" s="2">
+      <c r="D298">
         <v>150000</v>
       </c>
     </row>
@@ -4613,13 +4612,13 @@
       <c r="A299" s="1">
         <v>2899</v>
       </c>
-      <c r="B299" s="2">
+      <c r="B299">
         <v>1996</v>
       </c>
-      <c r="C299" s="2">
+      <c r="C299">
         <v>69</v>
       </c>
-      <c r="D299" s="2">
+      <c r="D299">
         <v>150000</v>
       </c>
     </row>
@@ -4627,13 +4626,13 @@
       <c r="A300" s="1">
         <v>4800</v>
       </c>
-      <c r="B300" s="2">
+      <c r="B300">
         <v>2004</v>
       </c>
-      <c r="C300" s="2">
+      <c r="C300">
         <v>75</v>
       </c>
-      <c r="D300" s="2">
+      <c r="D300">
         <v>80000</v>
       </c>
     </row>
@@ -4641,13 +4640,13 @@
       <c r="A301" s="1">
         <v>6799</v>
       </c>
-      <c r="B301" s="2">
+      <c r="B301">
         <v>2008</v>
       </c>
-      <c r="C301" s="2">
+      <c r="C301">
         <v>174</v>
       </c>
-      <c r="D301" s="2">
+      <c r="D301">
         <v>90000</v>
       </c>
     </row>
@@ -4655,13 +4654,13 @@
       <c r="A302" s="1">
         <v>3400</v>
       </c>
-      <c r="B302" s="2">
+      <c r="B302">
         <v>2003</v>
       </c>
-      <c r="C302" s="2">
+      <c r="C302">
         <v>100</v>
       </c>
-      <c r="D302" s="2">
+      <c r="D302">
         <v>150000</v>
       </c>
     </row>
@@ -4669,13 +4668,13 @@
       <c r="A303" s="1">
         <v>2650</v>
       </c>
-      <c r="B303" s="2">
+      <c r="B303">
         <v>2004</v>
       </c>
-      <c r="C303" s="2">
+      <c r="C303">
         <v>125</v>
       </c>
-      <c r="D303" s="2">
+      <c r="D303">
         <v>150000</v>
       </c>
     </row>
@@ -4683,13 +4682,13 @@
       <c r="A304" s="1">
         <v>1000</v>
       </c>
-      <c r="B304" s="2">
+      <c r="B304">
         <v>1999</v>
       </c>
-      <c r="C304" s="2">
+      <c r="C304">
         <v>107</v>
       </c>
-      <c r="D304" s="2">
+      <c r="D304">
         <v>150000</v>
       </c>
     </row>
@@ -4697,13 +4696,13 @@
       <c r="A305" s="1">
         <v>800</v>
       </c>
-      <c r="B305" s="2">
+      <c r="B305">
         <v>1997</v>
       </c>
-      <c r="C305" s="2">
+      <c r="C305">
         <v>125</v>
       </c>
-      <c r="D305" s="2">
+      <c r="D305">
         <v>150000</v>
       </c>
     </row>
@@ -4711,13 +4710,13 @@
       <c r="A306" s="1">
         <v>5299</v>
       </c>
-      <c r="B306" s="2">
+      <c r="B306">
         <v>2002</v>
       </c>
-      <c r="C306" s="2">
+      <c r="C306">
         <v>220</v>
       </c>
-      <c r="D306" s="2">
+      <c r="D306">
         <v>150000</v>
       </c>
     </row>
@@ -4725,13 +4724,13 @@
       <c r="A307" s="1">
         <v>7150</v>
       </c>
-      <c r="B307" s="2">
+      <c r="B307">
         <v>2002</v>
       </c>
-      <c r="C307" s="2">
+      <c r="C307">
         <v>150</v>
       </c>
-      <c r="D307" s="2">
+      <c r="D307">
         <v>150000</v>
       </c>
     </row>
@@ -4739,13 +4738,13 @@
       <c r="A308" s="1">
         <v>200</v>
       </c>
-      <c r="B308" s="2">
+      <c r="B308">
         <v>2009</v>
       </c>
-      <c r="C308" s="2">
+      <c r="C308">
         <v>0</v>
       </c>
-      <c r="D308" s="2">
+      <c r="D308">
         <v>10000</v>
       </c>
     </row>
@@ -4753,13 +4752,13 @@
       <c r="A309" s="1">
         <v>2300</v>
       </c>
-      <c r="B309" s="2">
+      <c r="B309">
         <v>2006</v>
       </c>
-      <c r="C309" s="2">
+      <c r="C309">
         <v>88</v>
       </c>
-      <c r="D309" s="2">
+      <c r="D309">
         <v>150000</v>
       </c>
     </row>
@@ -4767,13 +4766,13 @@
       <c r="A310" s="1">
         <v>1600</v>
       </c>
-      <c r="B310" s="2">
+      <c r="B310">
         <v>1999</v>
       </c>
-      <c r="C310" s="2">
+      <c r="C310">
         <v>0</v>
       </c>
-      <c r="D310" s="2">
+      <c r="D310">
         <v>150000</v>
       </c>
     </row>
@@ -4781,13 +4780,13 @@
       <c r="A311" s="1">
         <v>350</v>
       </c>
-      <c r="B311" s="2">
+      <c r="B311">
         <v>2017</v>
       </c>
-      <c r="C311" s="2">
+      <c r="C311">
         <v>0</v>
       </c>
-      <c r="D311" s="2">
+      <c r="D311">
         <v>150000</v>
       </c>
     </row>
@@ -4795,13 +4794,13 @@
       <c r="A312" s="1">
         <v>5500</v>
       </c>
-      <c r="B312" s="2">
+      <c r="B312">
         <v>2006</v>
       </c>
-      <c r="C312" s="2">
+      <c r="C312">
         <v>140</v>
       </c>
-      <c r="D312" s="2">
+      <c r="D312">
         <v>150000</v>
       </c>
     </row>
@@ -4809,13 +4808,13 @@
       <c r="A313" s="1">
         <v>4400</v>
       </c>
-      <c r="B313" s="2">
+      <c r="B313">
         <v>1997</v>
       </c>
-      <c r="C313" s="2">
+      <c r="C313">
         <v>54</v>
       </c>
-      <c r="D313" s="2">
+      <c r="D313">
         <v>125000</v>
       </c>
     </row>
@@ -4823,13 +4822,13 @@
       <c r="A314" s="1">
         <v>7950</v>
       </c>
-      <c r="B314" s="2">
+      <c r="B314">
         <v>2008</v>
       </c>
-      <c r="C314" s="2">
+      <c r="C314">
         <v>140</v>
       </c>
-      <c r="D314" s="2">
+      <c r="D314">
         <v>150000</v>
       </c>
     </row>
@@ -4837,13 +4836,13 @@
       <c r="A315" s="1">
         <v>16500</v>
       </c>
-      <c r="B315" s="2">
+      <c r="B315">
         <v>2007</v>
       </c>
-      <c r="C315" s="2">
+      <c r="C315">
         <v>265</v>
       </c>
-      <c r="D315" s="2">
+      <c r="D315">
         <v>150000</v>
       </c>
     </row>
@@ -4851,13 +4850,13 @@
       <c r="A316" s="1">
         <v>8100</v>
       </c>
-      <c r="B316" s="2">
+      <c r="B316">
         <v>2004</v>
       </c>
-      <c r="C316" s="2">
+      <c r="C316">
         <v>170</v>
       </c>
-      <c r="D316" s="2">
+      <c r="D316">
         <v>150000</v>
       </c>
     </row>
@@ -4865,13 +4864,13 @@
       <c r="A317" s="1">
         <v>3999</v>
       </c>
-      <c r="B317" s="2">
+      <c r="B317">
         <v>2017</v>
       </c>
-      <c r="C317" s="2">
+      <c r="C317">
         <v>85</v>
       </c>
-      <c r="D317" s="2">
+      <c r="D317">
         <v>150000</v>
       </c>
     </row>
@@ -4879,13 +4878,13 @@
       <c r="A318" s="1">
         <v>9750</v>
       </c>
-      <c r="B318" s="2">
+      <c r="B318">
         <v>2013</v>
       </c>
-      <c r="C318" s="2">
+      <c r="C318">
         <v>75</v>
       </c>
-      <c r="D318" s="2">
+      <c r="D318">
         <v>60000</v>
       </c>
     </row>
@@ -4893,13 +4892,13 @@
       <c r="A319" s="1">
         <v>7700</v>
       </c>
-      <c r="B319" s="2">
+      <c r="B319">
         <v>2009</v>
       </c>
-      <c r="C319" s="2">
+      <c r="C319">
         <v>185</v>
       </c>
-      <c r="D319" s="2">
+      <c r="D319">
         <v>150000</v>
       </c>
     </row>
@@ -4907,13 +4906,13 @@
       <c r="A320" s="1">
         <v>2500</v>
       </c>
-      <c r="B320" s="2">
+      <c r="B320">
         <v>1999</v>
       </c>
-      <c r="C320" s="2">
+      <c r="C320">
         <v>88</v>
       </c>
-      <c r="D320" s="2">
+      <c r="D320">
         <v>150000</v>
       </c>
     </row>
@@ -4921,13 +4920,13 @@
       <c r="A321" s="1">
         <v>1195</v>
       </c>
-      <c r="B321" s="2">
+      <c r="B321">
         <v>1999</v>
       </c>
-      <c r="C321" s="2">
+      <c r="C321">
         <v>54</v>
       </c>
-      <c r="D321" s="2">
+      <c r="D321">
         <v>125000</v>
       </c>
     </row>
@@ -4935,13 +4934,13 @@
       <c r="A322" s="1">
         <v>9790</v>
       </c>
-      <c r="B322" s="2">
+      <c r="B322">
         <v>2014</v>
       </c>
-      <c r="C322" s="2">
+      <c r="C322">
         <v>73</v>
       </c>
-      <c r="D322" s="2">
+      <c r="D322">
         <v>30000</v>
       </c>
     </row>
@@ -4949,13 +4948,13 @@
       <c r="A323" s="1">
         <v>1849</v>
       </c>
-      <c r="B323" s="2">
+      <c r="B323">
         <v>1999</v>
       </c>
-      <c r="C323" s="2">
+      <c r="C323">
         <v>54</v>
       </c>
-      <c r="D323" s="2">
+      <c r="D323">
         <v>90000</v>
       </c>
     </row>
@@ -4963,13 +4962,13 @@
       <c r="A324" s="1">
         <v>3300</v>
       </c>
-      <c r="B324" s="2">
+      <c r="B324">
         <v>2006</v>
       </c>
-      <c r="C324" s="2">
+      <c r="C324">
         <v>41</v>
       </c>
-      <c r="D324" s="2">
+      <c r="D324">
         <v>125000</v>
       </c>
     </row>
@@ -4977,13 +4976,13 @@
       <c r="A325" s="1">
         <v>650</v>
       </c>
-      <c r="B325" s="2">
+      <c r="B325">
         <v>1991</v>
       </c>
-      <c r="C325" s="2">
+      <c r="C325">
         <v>77</v>
       </c>
-      <c r="D325" s="2">
+      <c r="D325">
         <v>150000</v>
       </c>
     </row>
@@ -4991,13 +4990,13 @@
       <c r="A326" s="1">
         <v>2600</v>
       </c>
-      <c r="B326" s="2">
+      <c r="B326">
         <v>1998</v>
       </c>
-      <c r="C326" s="2">
+      <c r="C326">
         <v>170</v>
       </c>
-      <c r="D326" s="2">
+      <c r="D326">
         <v>150000</v>
       </c>
     </row>
@@ -5005,13 +5004,13 @@
       <c r="A327" s="1">
         <v>11700</v>
       </c>
-      <c r="B327" s="2">
+      <c r="B327">
         <v>2008</v>
       </c>
-      <c r="C327" s="2">
+      <c r="C327">
         <v>170</v>
       </c>
-      <c r="D327" s="2">
+      <c r="D327">
         <v>150000</v>
       </c>
     </row>
@@ -5019,13 +5018,13 @@
       <c r="A328" s="1">
         <v>600</v>
       </c>
-      <c r="B328" s="2">
+      <c r="B328">
         <v>1998</v>
       </c>
-      <c r="C328" s="2">
+      <c r="C328">
         <v>90</v>
       </c>
-      <c r="D328" s="2">
+      <c r="D328">
         <v>150000</v>
       </c>
     </row>
@@ -5033,13 +5032,13 @@
       <c r="A329" s="1">
         <v>4950</v>
       </c>
-      <c r="B329" s="2">
+      <c r="B329">
         <v>2009</v>
       </c>
-      <c r="C329" s="2">
+      <c r="C329">
         <v>109</v>
       </c>
-      <c r="D329" s="2">
+      <c r="D329">
         <v>150000</v>
       </c>
     </row>
@@ -5047,13 +5046,13 @@
       <c r="A330" s="1">
         <v>1600</v>
       </c>
-      <c r="B330" s="2">
+      <c r="B330">
         <v>2003</v>
       </c>
-      <c r="C330" s="2">
+      <c r="C330">
         <v>50</v>
       </c>
-      <c r="D330" s="2">
+      <c r="D330">
         <v>150000</v>
       </c>
     </row>
@@ -5061,13 +5060,13 @@
       <c r="A331" s="1">
         <v>8499</v>
       </c>
-      <c r="B331" s="2">
+      <c r="B331">
         <v>2006</v>
       </c>
-      <c r="C331" s="2">
+      <c r="C331">
         <v>150</v>
       </c>
-      <c r="D331" s="2">
+      <c r="D331">
         <v>150000</v>
       </c>
     </row>
@@ -5075,13 +5074,13 @@
       <c r="A332" s="1">
         <v>1650</v>
       </c>
-      <c r="B332" s="2">
+      <c r="B332">
         <v>2017</v>
       </c>
-      <c r="C332" s="2">
+      <c r="C332">
         <v>0</v>
       </c>
-      <c r="D332" s="2">
+      <c r="D332">
         <v>60000</v>
       </c>
     </row>
@@ -5089,13 +5088,13 @@
       <c r="A333" s="1">
         <v>1700</v>
       </c>
-      <c r="B333" s="2">
+      <c r="B333">
         <v>1999</v>
       </c>
-      <c r="C333" s="2">
+      <c r="C333">
         <v>101</v>
       </c>
-      <c r="D333" s="2">
+      <c r="D333">
         <v>150000</v>
       </c>
     </row>
@@ -5103,13 +5102,13 @@
       <c r="A334" s="1">
         <v>5750</v>
       </c>
-      <c r="B334" s="2">
+      <c r="B334">
         <v>2010</v>
       </c>
-      <c r="C334" s="2">
+      <c r="C334">
         <v>90</v>
       </c>
-      <c r="D334" s="2">
+      <c r="D334">
         <v>100000</v>
       </c>
     </row>
@@ -5117,13 +5116,13 @@
       <c r="A335" s="1">
         <v>600</v>
       </c>
-      <c r="B335" s="2">
+      <c r="B335">
         <v>2001</v>
       </c>
-      <c r="C335" s="2">
+      <c r="C335">
         <v>75</v>
       </c>
-      <c r="D335" s="2">
+      <c r="D335">
         <v>150000</v>
       </c>
     </row>
@@ -5131,13 +5130,13 @@
       <c r="A336" s="1">
         <v>0</v>
       </c>
-      <c r="B336" s="2">
+      <c r="B336">
         <v>2005</v>
       </c>
-      <c r="C336" s="2">
+      <c r="C336">
         <v>0</v>
       </c>
-      <c r="D336" s="2">
+      <c r="D336">
         <v>150000</v>
       </c>
     </row>
@@ -5145,13 +5144,13 @@
       <c r="A337" s="1">
         <v>8700</v>
       </c>
-      <c r="B337" s="2">
+      <c r="B337">
         <v>2004</v>
       </c>
-      <c r="C337" s="2">
+      <c r="C337">
         <v>170</v>
       </c>
-      <c r="D337" s="2">
+      <c r="D337">
         <v>150000</v>
       </c>
     </row>
@@ -5159,13 +5158,13 @@
       <c r="A338" s="1">
         <v>1200</v>
       </c>
-      <c r="B338" s="2">
+      <c r="B338">
         <v>1999</v>
       </c>
-      <c r="C338" s="2">
+      <c r="C338">
         <v>125</v>
       </c>
-      <c r="D338" s="2">
+      <c r="D338">
         <v>150000</v>
       </c>
     </row>
@@ -5173,13 +5172,13 @@
       <c r="A339" s="1">
         <v>18880</v>
       </c>
-      <c r="B339" s="2">
+      <c r="B339">
         <v>2014</v>
       </c>
-      <c r="C339" s="2">
+      <c r="C339">
         <v>116</v>
       </c>
-      <c r="D339" s="2">
+      <c r="D339">
         <v>20000</v>
       </c>
     </row>
@@ -5187,13 +5186,13 @@
       <c r="A340" s="1">
         <v>11200</v>
       </c>
-      <c r="B340" s="2">
+      <c r="B340">
         <v>2008</v>
       </c>
-      <c r="C340" s="2">
+      <c r="C340">
         <v>177</v>
       </c>
-      <c r="D340" s="2">
+      <c r="D340">
         <v>150000</v>
       </c>
     </row>
@@ -5201,13 +5200,13 @@
       <c r="A341" s="1">
         <v>3550</v>
       </c>
-      <c r="B341" s="2">
+      <c r="B341">
         <v>1993</v>
       </c>
-      <c r="C341" s="2">
+      <c r="C341">
         <v>0</v>
       </c>
-      <c r="D341" s="2">
+      <c r="D341">
         <v>125000</v>
       </c>
     </row>
@@ -5215,13 +5214,13 @@
       <c r="A342" s="1">
         <v>3900</v>
       </c>
-      <c r="B342" s="2">
+      <c r="B342">
         <v>2003</v>
       </c>
-      <c r="C342" s="2">
+      <c r="C342">
         <v>75</v>
       </c>
-      <c r="D342" s="2">
+      <c r="D342">
         <v>125000</v>
       </c>
     </row>
@@ -5229,13 +5228,13 @@
       <c r="A343" s="1">
         <v>13849</v>
       </c>
-      <c r="B343" s="2">
+      <c r="B343">
         <v>2010</v>
       </c>
-      <c r="C343" s="2">
+      <c r="C343">
         <v>143</v>
       </c>
-      <c r="D343" s="2">
+      <c r="D343">
         <v>80000</v>
       </c>
     </row>
@@ -5243,13 +5242,13 @@
       <c r="A344" s="1">
         <v>13200</v>
       </c>
-      <c r="B344" s="2">
+      <c r="B344">
         <v>2013</v>
       </c>
-      <c r="C344" s="2">
+      <c r="C344">
         <v>105</v>
       </c>
-      <c r="D344" s="2">
+      <c r="D344">
         <v>40000</v>
       </c>
     </row>
@@ -5257,13 +5256,13 @@
       <c r="A345" s="1">
         <v>2500</v>
       </c>
-      <c r="B345" s="2">
+      <c r="B345">
         <v>2001</v>
       </c>
-      <c r="C345" s="2">
+      <c r="C345">
         <v>101</v>
       </c>
-      <c r="D345" s="2">
+      <c r="D345">
         <v>125000</v>
       </c>
     </row>
@@ -5271,13 +5270,13 @@
       <c r="A346" s="1">
         <v>2550</v>
       </c>
-      <c r="B346" s="2">
+      <c r="B346">
         <v>2006</v>
       </c>
-      <c r="C346" s="2">
+      <c r="C346">
         <v>54</v>
       </c>
-      <c r="D346" s="2">
+      <c r="D346">
         <v>150000</v>
       </c>
     </row>
@@ -5285,13 +5284,13 @@
       <c r="A347" s="1">
         <v>3900</v>
       </c>
-      <c r="B347" s="2">
+      <c r="B347">
         <v>2006</v>
       </c>
-      <c r="C347" s="2">
+      <c r="C347">
         <v>102</v>
       </c>
-      <c r="D347" s="2">
+      <c r="D347">
         <v>150000</v>
       </c>
     </row>
@@ -5299,13 +5298,13 @@
       <c r="A348" s="1">
         <v>2450</v>
       </c>
-      <c r="B348" s="2">
+      <c r="B348">
         <v>2001</v>
       </c>
-      <c r="C348" s="2">
+      <c r="C348">
         <v>231</v>
       </c>
-      <c r="D348" s="2">
+      <c r="D348">
         <v>150000</v>
       </c>
     </row>
@@ -5313,13 +5312,13 @@
       <c r="A349" s="1">
         <v>500</v>
       </c>
-      <c r="B349" s="2">
+      <c r="B349">
         <v>1996</v>
       </c>
-      <c r="C349" s="2">
+      <c r="C349">
         <v>45</v>
       </c>
-      <c r="D349" s="2">
+      <c r="D349">
         <v>70000</v>
       </c>
     </row>
@@ -5327,13 +5326,13 @@
       <c r="A350" s="1">
         <v>750</v>
       </c>
-      <c r="B350" s="2">
+      <c r="B350">
         <v>1998</v>
       </c>
-      <c r="C350" s="2">
+      <c r="C350">
         <v>90</v>
       </c>
-      <c r="D350" s="2">
+      <c r="D350">
         <v>150000</v>
       </c>
     </row>
@@ -5341,13 +5340,13 @@
       <c r="A351" s="1">
         <v>1799</v>
       </c>
-      <c r="B351" s="2">
+      <c r="B351">
         <v>1999</v>
       </c>
-      <c r="C351" s="2">
+      <c r="C351">
         <v>116</v>
       </c>
-      <c r="D351" s="2">
+      <c r="D351">
         <v>150000</v>
       </c>
     </row>
@@ -5355,13 +5354,13 @@
       <c r="A352" s="1">
         <v>950</v>
       </c>
-      <c r="B352" s="2">
+      <c r="B352">
         <v>1997</v>
       </c>
-      <c r="C352" s="2">
+      <c r="C352">
         <v>0</v>
       </c>
-      <c r="D352" s="2">
+      <c r="D352">
         <v>150000</v>
       </c>
     </row>
@@ -5369,13 +5368,13 @@
       <c r="A353" s="1">
         <v>8150</v>
       </c>
-      <c r="B353" s="2">
+      <c r="B353">
         <v>2012</v>
       </c>
-      <c r="C353" s="2">
+      <c r="C353">
         <v>75</v>
       </c>
-      <c r="D353" s="2">
+      <c r="D353">
         <v>60000</v>
       </c>
     </row>
@@ -5383,13 +5382,13 @@
       <c r="A354" s="1">
         <v>3900</v>
       </c>
-      <c r="B354" s="2">
+      <c r="B354">
         <v>2004</v>
       </c>
-      <c r="C354" s="2">
+      <c r="C354">
         <v>192</v>
       </c>
-      <c r="D354" s="2">
+      <c r="D354">
         <v>125000</v>
       </c>
     </row>
@@ -5397,13 +5396,13 @@
       <c r="A355" s="1">
         <v>5500</v>
       </c>
-      <c r="B355" s="2">
+      <c r="B355">
         <v>2012</v>
       </c>
-      <c r="C355" s="2">
+      <c r="C355">
         <v>68</v>
       </c>
-      <c r="D355" s="2">
+      <c r="D355">
         <v>40000</v>
       </c>
     </row>
@@ -5411,13 +5410,13 @@
       <c r="A356" s="1">
         <v>9999</v>
       </c>
-      <c r="B356" s="2">
+      <c r="B356">
         <v>2014</v>
       </c>
-      <c r="C356" s="2">
+      <c r="C356">
         <v>90</v>
       </c>
-      <c r="D356" s="2">
+      <c r="D356">
         <v>20000</v>
       </c>
     </row>
@@ -5425,13 +5424,13 @@
       <c r="A357" s="1">
         <v>1050</v>
       </c>
-      <c r="B357" s="2">
+      <c r="B357">
         <v>2018</v>
       </c>
-      <c r="C357" s="2">
+      <c r="C357">
         <v>0</v>
       </c>
-      <c r="D357" s="2">
+      <c r="D357">
         <v>150000</v>
       </c>
     </row>
@@ -5439,13 +5438,13 @@
       <c r="A358" s="1">
         <v>500</v>
       </c>
-      <c r="B358" s="2">
+      <c r="B358">
         <v>2001</v>
       </c>
-      <c r="C358" s="2">
+      <c r="C358">
         <v>131</v>
       </c>
-      <c r="D358" s="2">
+      <c r="D358">
         <v>150000</v>
       </c>
     </row>
@@ -5453,13 +5452,13 @@
       <c r="A359" s="1">
         <v>699</v>
       </c>
-      <c r="B359" s="2">
+      <c r="B359">
         <v>1992</v>
       </c>
-      <c r="C359" s="2">
+      <c r="C359">
         <v>66</v>
       </c>
-      <c r="D359" s="2">
+      <c r="D359">
         <v>150000</v>
       </c>
     </row>
@@ -5467,13 +5466,13 @@
       <c r="A360" s="1">
         <v>999</v>
       </c>
-      <c r="B360" s="2">
+      <c r="B360">
         <v>1994</v>
       </c>
-      <c r="C360" s="2">
+      <c r="C360">
         <v>115</v>
       </c>
-      <c r="D360" s="2">
+      <c r="D360">
         <v>150000</v>
       </c>
     </row>
@@ -5481,13 +5480,13 @@
       <c r="A361" s="1">
         <v>6250</v>
       </c>
-      <c r="B361" s="2">
+      <c r="B361">
         <v>2003</v>
       </c>
-      <c r="C361" s="2">
+      <c r="C361">
         <v>299</v>
       </c>
-      <c r="D361" s="2">
+      <c r="D361">
         <v>150000</v>
       </c>
     </row>
@@ -5495,13 +5494,13 @@
       <c r="A362" s="1">
         <v>10000</v>
       </c>
-      <c r="B362" s="2">
+      <c r="B362">
         <v>1976</v>
       </c>
-      <c r="C362" s="2">
+      <c r="C362">
         <v>0</v>
       </c>
-      <c r="D362" s="2">
+      <c r="D362">
         <v>5000</v>
       </c>
     </row>
@@ -5509,13 +5508,13 @@
       <c r="A363" s="1">
         <v>300</v>
       </c>
-      <c r="B363" s="2">
+      <c r="B363">
         <v>2001</v>
       </c>
-      <c r="C363" s="2">
+      <c r="C363">
         <v>0</v>
       </c>
-      <c r="D363" s="2">
+      <c r="D363">
         <v>150000</v>
       </c>
     </row>
@@ -5523,13 +5522,13 @@
       <c r="A364" s="1">
         <v>16500</v>
       </c>
-      <c r="B364" s="2">
+      <c r="B364">
         <v>1983</v>
       </c>
-      <c r="C364" s="2">
+      <c r="C364">
         <v>218</v>
       </c>
-      <c r="D364" s="2">
+      <c r="D364">
         <v>150000</v>
       </c>
     </row>
@@ -5537,13 +5536,13 @@
       <c r="A365" s="1">
         <v>6500</v>
       </c>
-      <c r="B365" s="2">
+      <c r="B365">
         <v>2007</v>
       </c>
-      <c r="C365" s="2">
+      <c r="C365">
         <v>125</v>
       </c>
-      <c r="D365" s="2">
+      <c r="D365">
         <v>125000</v>
       </c>
     </row>
@@ -5551,13 +5550,13 @@
       <c r="A366" s="1">
         <v>1200</v>
       </c>
-      <c r="B366" s="2">
+      <c r="B366">
         <v>2016</v>
       </c>
-      <c r="C366" s="2">
+      <c r="C366">
         <v>75</v>
       </c>
-      <c r="D366" s="2">
+      <c r="D366">
         <v>150000</v>
       </c>
     </row>
@@ -5565,13 +5564,13 @@
       <c r="A367" s="1">
         <v>1480</v>
       </c>
-      <c r="B367" s="2">
+      <c r="B367">
         <v>2000</v>
       </c>
-      <c r="C367" s="2">
+      <c r="C367">
         <v>74</v>
       </c>
-      <c r="D367" s="2">
+      <c r="D367">
         <v>150000</v>
       </c>
     </row>
@@ -5579,13 +5578,13 @@
       <c r="A368" s="1">
         <v>1490</v>
       </c>
-      <c r="B368" s="2">
+      <c r="B368">
         <v>2000</v>
       </c>
-      <c r="C368" s="2">
+      <c r="C368">
         <v>60</v>
       </c>
-      <c r="D368" s="2">
+      <c r="D368">
         <v>100000</v>
       </c>
     </row>
@@ -5593,13 +5592,13 @@
       <c r="A369" s="1">
         <v>3200</v>
       </c>
-      <c r="B369" s="2">
+      <c r="B369">
         <v>2008</v>
       </c>
-      <c r="C369" s="2">
+      <c r="C369">
         <v>110</v>
       </c>
-      <c r="D369" s="2">
+      <c r="D369">
         <v>150000</v>
       </c>
     </row>
@@ -5607,13 +5606,13 @@
       <c r="A370" s="1">
         <v>3250</v>
       </c>
-      <c r="B370" s="2">
+      <c r="B370">
         <v>2003</v>
       </c>
-      <c r="C370" s="2">
+      <c r="C370">
         <v>163</v>
       </c>
-      <c r="D370" s="2">
+      <c r="D370">
         <v>150000</v>
       </c>
     </row>
@@ -5621,13 +5620,13 @@
       <c r="A371" s="1">
         <v>3400</v>
       </c>
-      <c r="B371" s="2">
+      <c r="B371">
         <v>2006</v>
       </c>
-      <c r="C371" s="2">
+      <c r="C371">
         <v>54</v>
       </c>
-      <c r="D371" s="2">
+      <c r="D371">
         <v>70000</v>
       </c>
     </row>
@@ -5635,13 +5634,13 @@
       <c r="A372" s="1">
         <v>1100</v>
       </c>
-      <c r="B372" s="2">
+      <c r="B372">
         <v>2002</v>
       </c>
-      <c r="C372" s="2">
+      <c r="C372">
         <v>58</v>
       </c>
-      <c r="D372" s="2">
+      <c r="D372">
         <v>150000</v>
       </c>
     </row>
@@ -5649,13 +5648,13 @@
       <c r="A373" s="1">
         <v>1750</v>
       </c>
-      <c r="B373" s="2">
+      <c r="B373">
         <v>2002</v>
       </c>
-      <c r="C373" s="2">
+      <c r="C373">
         <v>125</v>
       </c>
-      <c r="D373" s="2">
+      <c r="D373">
         <v>150000</v>
       </c>
     </row>
@@ -5663,13 +5662,13 @@
       <c r="A374" s="1">
         <v>3300</v>
       </c>
-      <c r="B374" s="2">
+      <c r="B374">
         <v>2006</v>
       </c>
-      <c r="C374" s="2">
+      <c r="C374">
         <v>140</v>
       </c>
-      <c r="D374" s="2">
+      <c r="D374">
         <v>150000</v>
       </c>
     </row>
@@ -5677,13 +5676,13 @@
       <c r="A375" s="1">
         <v>1350</v>
       </c>
-      <c r="B375" s="2">
+      <c r="B375">
         <v>2005</v>
       </c>
-      <c r="C375" s="2">
+      <c r="C375">
         <v>52</v>
       </c>
-      <c r="D375" s="2">
+      <c r="D375">
         <v>150000</v>
       </c>
     </row>
@@ -5691,13 +5690,13 @@
       <c r="A376" s="1">
         <v>8250</v>
       </c>
-      <c r="B376" s="2">
+      <c r="B376">
         <v>2012</v>
       </c>
-      <c r="C376" s="2">
+      <c r="C376">
         <v>69</v>
       </c>
-      <c r="D376" s="2">
+      <c r="D376">
         <v>80000</v>
       </c>
     </row>
@@ -5705,13 +5704,13 @@
       <c r="A377" s="1">
         <v>2500</v>
       </c>
-      <c r="B377" s="2">
+      <c r="B377">
         <v>2000</v>
       </c>
-      <c r="C377" s="2">
+      <c r="C377">
         <v>115</v>
       </c>
-      <c r="D377" s="2">
+      <c r="D377">
         <v>150000</v>
       </c>
     </row>
@@ -5719,13 +5718,13 @@
       <c r="A378" s="1">
         <v>3999</v>
       </c>
-      <c r="B378" s="2">
+      <c r="B378">
         <v>2004</v>
       </c>
-      <c r="C378" s="2">
+      <c r="C378">
         <v>163</v>
       </c>
-      <c r="D378" s="2">
+      <c r="D378">
         <v>150000</v>
       </c>
     </row>
@@ -5733,13 +5732,13 @@
       <c r="A379" s="1">
         <v>7000</v>
       </c>
-      <c r="B379" s="2">
+      <c r="B379">
         <v>2007</v>
       </c>
-      <c r="C379" s="2">
+      <c r="C379">
         <v>143</v>
       </c>
-      <c r="D379" s="2">
+      <c r="D379">
         <v>150000</v>
       </c>
     </row>
@@ -5747,13 +5746,13 @@
       <c r="A380" s="1">
         <v>2950</v>
       </c>
-      <c r="B380" s="2">
+      <c r="B380">
         <v>2005</v>
       </c>
-      <c r="C380" s="2">
+      <c r="C380">
         <v>131</v>
       </c>
-      <c r="D380" s="2">
+      <c r="D380">
         <v>150000</v>
       </c>
     </row>
@@ -5761,13 +5760,13 @@
       <c r="A381" s="1">
         <v>4850</v>
       </c>
-      <c r="B381" s="2">
+      <c r="B381">
         <v>2010</v>
       </c>
-      <c r="C381" s="2">
+      <c r="C381">
         <v>77</v>
       </c>
-      <c r="D381" s="2">
+      <c r="D381">
         <v>100000</v>
       </c>
     </row>
@@ -5775,13 +5774,13 @@
       <c r="A382" s="1">
         <v>1100</v>
       </c>
-      <c r="B382" s="2">
+      <c r="B382">
         <v>2000</v>
       </c>
-      <c r="C382" s="2">
+      <c r="C382">
         <v>60</v>
       </c>
-      <c r="D382" s="2">
+      <c r="D382">
         <v>60000</v>
       </c>
     </row>
@@ -5789,13 +5788,13 @@
       <c r="A383" s="1">
         <v>3600</v>
       </c>
-      <c r="B383" s="2">
+      <c r="B383">
         <v>2003</v>
       </c>
-      <c r="C383" s="2">
+      <c r="C383">
         <v>147</v>
       </c>
-      <c r="D383" s="2">
+      <c r="D383">
         <v>125000</v>
       </c>
     </row>
@@ -5803,13 +5802,13 @@
       <c r="A384" s="1">
         <v>7750</v>
       </c>
-      <c r="B384" s="2">
+      <c r="B384">
         <v>2009</v>
       </c>
-      <c r="C384" s="2">
+      <c r="C384">
         <v>80</v>
       </c>
-      <c r="D384" s="2">
+      <c r="D384">
         <v>125000</v>
       </c>
     </row>
@@ -5817,13 +5816,13 @@
       <c r="A385" s="1">
         <v>2950</v>
       </c>
-      <c r="B385" s="2">
+      <c r="B385">
         <v>2004</v>
       </c>
-      <c r="C385" s="2">
+      <c r="C385">
         <v>54</v>
       </c>
-      <c r="D385" s="2">
+      <c r="D385">
         <v>90000</v>
       </c>
     </row>
@@ -5831,13 +5830,13 @@
       <c r="A386" s="1">
         <v>400</v>
       </c>
-      <c r="B386" s="2">
+      <c r="B386">
         <v>2017</v>
       </c>
-      <c r="C386" s="2">
+      <c r="C386">
         <v>65</v>
       </c>
-      <c r="D386" s="2">
+      <c r="D386">
         <v>150000</v>
       </c>
     </row>
@@ -5845,13 +5844,13 @@
       <c r="A387" s="1">
         <v>6880</v>
       </c>
-      <c r="B387" s="2">
+      <c r="B387">
         <v>2007</v>
       </c>
-      <c r="C387" s="2">
+      <c r="C387">
         <v>150</v>
       </c>
-      <c r="D387" s="2">
+      <c r="D387">
         <v>150000</v>
       </c>
     </row>
@@ -5859,13 +5858,13 @@
       <c r="A388" s="1">
         <v>5600</v>
       </c>
-      <c r="B388" s="2">
+      <c r="B388">
         <v>2008</v>
       </c>
-      <c r="C388" s="2">
+      <c r="C388">
         <v>140</v>
       </c>
-      <c r="D388" s="2">
+      <c r="D388">
         <v>150000</v>
       </c>
     </row>
@@ -5873,13 +5872,13 @@
       <c r="A389" s="1">
         <v>10550</v>
       </c>
-      <c r="B389" s="2">
+      <c r="B389">
         <v>2012</v>
       </c>
-      <c r="C389" s="2">
+      <c r="C389">
         <v>105</v>
       </c>
-      <c r="D389" s="2">
+      <c r="D389">
         <v>60000</v>
       </c>
     </row>
@@ -5887,13 +5886,13 @@
       <c r="A390" s="1">
         <v>17500</v>
       </c>
-      <c r="B390" s="2">
+      <c r="B390">
         <v>2013</v>
       </c>
-      <c r="C390" s="2">
+      <c r="C390">
         <v>122</v>
       </c>
-      <c r="D390" s="2">
+      <c r="D390">
         <v>40000</v>
       </c>
     </row>
@@ -5901,13 +5900,13 @@
       <c r="A391" s="1">
         <v>999</v>
       </c>
-      <c r="B391" s="2">
+      <c r="B391">
         <v>1999</v>
       </c>
-      <c r="C391" s="2">
+      <c r="C391">
         <v>60</v>
       </c>
-      <c r="D391" s="2">
+      <c r="D391">
         <v>150000</v>
       </c>
     </row>
@@ -5915,13 +5914,13 @@
       <c r="A392" s="1">
         <v>3400</v>
       </c>
-      <c r="B392" s="2">
+      <c r="B392">
         <v>2018</v>
       </c>
-      <c r="C392" s="2">
+      <c r="C392">
         <v>0</v>
       </c>
-      <c r="D392" s="2">
+      <c r="D392">
         <v>150000</v>
       </c>
     </row>
@@ -5929,13 +5928,13 @@
       <c r="A393" s="1">
         <v>2000</v>
       </c>
-      <c r="B393" s="2">
+      <c r="B393">
         <v>1998</v>
       </c>
-      <c r="C393" s="2">
+      <c r="C393">
         <v>115</v>
       </c>
-      <c r="D393" s="2">
+      <c r="D393">
         <v>150000</v>
       </c>
     </row>
@@ -5943,13 +5942,13 @@
       <c r="A394" s="1">
         <v>2350</v>
       </c>
-      <c r="B394" s="2">
+      <c r="B394">
         <v>2006</v>
       </c>
-      <c r="C394" s="2">
+      <c r="C394">
         <v>0</v>
       </c>
-      <c r="D394" s="2">
+      <c r="D394">
         <v>5000</v>
       </c>
     </row>
@@ -5957,13 +5956,13 @@
       <c r="A395" s="1">
         <v>6250</v>
       </c>
-      <c r="B395" s="2">
+      <c r="B395">
         <v>2016</v>
       </c>
-      <c r="C395" s="2">
+      <c r="C395">
         <v>310</v>
       </c>
-      <c r="D395" s="2">
+      <c r="D395">
         <v>150000</v>
       </c>
     </row>
